--- a/results/tables/ber_vs_rx_bw.xlsx
+++ b/results/tables/ber_vs_rx_bw.xlsx
@@ -1308,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1342,6 +1342,11 @@
           <t>Q</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EVM</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1354,13 +1359,16 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1626953907815631</v>
+        <v>0.1616547497446374</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1523020956798583</v>
+        <v>0.1499808023669701</v>
       </c>
       <c r="F2" t="n">
-        <v>1.026609898085201</v>
+        <v>1.036515730174347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>77.77146052542301</v>
       </c>
     </row>
     <row r="3">
@@ -1374,13 +1382,16 @@
         <v>4000000000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07936873747494989</v>
+        <v>0.08053115423901941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0785722100586511</v>
+        <v>0.07131597394936429</v>
       </c>
       <c r="F3" t="n">
-        <v>1.414741096703341</v>
+        <v>1.466059977276725</v>
+      </c>
+      <c r="G3" t="n">
+        <v>61.70821928731177</v>
       </c>
     </row>
     <row r="4">
@@ -1394,13 +1405,16 @@
         <v>5000000000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02129258517034068</v>
+        <v>0.02113381001021451</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02165708098488127</v>
+        <v>0.02426270557799858</v>
       </c>
       <c r="F4" t="n">
-        <v>2.020667831635807</v>
+        <v>1.972738079058338</v>
+      </c>
+      <c r="G4" t="n">
+        <v>47.78915244161028</v>
       </c>
     </row>
     <row r="5">
@@ -1414,13 +1428,16 @@
         <v>6000000000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01832665330661323</v>
+        <v>0.01811031664964249</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01862838331918308</v>
+        <v>0.01786706860100327</v>
       </c>
       <c r="F5" t="n">
-        <v>2.082939191923169</v>
+        <v>2.099939798673878</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47.08137782038047</v>
       </c>
     </row>
     <row r="6">
@@ -1434,13 +1451,16 @@
         <v>7000000000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01698396793587174</v>
+        <v>0.01745658835546476</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01752207142458976</v>
+        <v>0.01710913542104199</v>
       </c>
       <c r="F6" t="n">
-        <v>2.107847959847198</v>
+        <v>2.117490144685449</v>
+      </c>
+      <c r="G6" t="n">
+        <v>45.87992501324828</v>
       </c>
     </row>
     <row r="7">
@@ -1454,13 +1474,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01828657314629259</v>
+        <v>0.01845760980592441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01778410138328359</v>
+        <v>0.01808009806844265</v>
       </c>
       <c r="F7" t="n">
-        <v>2.101829628145391</v>
+        <v>2.095121466511104</v>
+      </c>
+      <c r="G7" t="n">
+        <v>46.63973598804056</v>
       </c>
     </row>
     <row r="8">
@@ -1474,13 +1497,16 @@
         <v>9000000000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0198997995991984</v>
+        <v>0.02117466802860061</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02028048663212676</v>
+        <v>0.02188491668654911</v>
       </c>
       <c r="F8" t="n">
-        <v>2.047990061135534</v>
+        <v>2.016288340878317</v>
+      </c>
+      <c r="G8" t="n">
+        <v>47.21122967166929</v>
       </c>
     </row>
     <row r="9">
@@ -1494,13 +1520,16 @@
         <v>10000000000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02490981963927856</v>
+        <v>0.02413687436159346</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02462204052865249</v>
+        <v>0.03036102750273187</v>
       </c>
       <c r="F9" t="n">
-        <v>1.96647228208034</v>
+        <v>1.87551392942494</v>
+      </c>
+      <c r="G9" t="n">
+        <v>48.97291248014096</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1543,16 @@
         <v>11000000000</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03162324649298597</v>
+        <v>0.03159346271705822</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03173289283001707</v>
+        <v>0.032213561319187</v>
       </c>
       <c r="F10" t="n">
-        <v>1.855914220869882</v>
+        <v>1.849212582011992</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51.48307233596475</v>
       </c>
     </row>
     <row r="11">
@@ -1534,13 +1566,16 @@
         <v>12000000000</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03950901803607215</v>
+        <v>0.04114402451481103</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04034189491893393</v>
+        <v>0.04595490338974317</v>
       </c>
       <c r="F11" t="n">
-        <v>1.74673227089737</v>
+        <v>1.685408386130841</v>
+      </c>
+      <c r="G11" t="n">
+        <v>54.36510286957819</v>
       </c>
     </row>
     <row r="12">
@@ -1554,13 +1589,16 @@
         <v>13000000000</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05017034068136272</v>
+        <v>0.05089887640449439</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04991767621265745</v>
+        <v>0.05206603166696692</v>
       </c>
       <c r="F12" t="n">
-        <v>1.645652360406957</v>
+        <v>1.625143136564266</v>
+      </c>
+      <c r="G12" t="n">
+        <v>58.84445896005837</v>
       </c>
     </row>
     <row r="13">
@@ -1574,13 +1612,16 @@
         <v>14000000000</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06013026052104208</v>
+        <v>0.06107252298263535</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05949170565581098</v>
+        <v>0.06541029362387392</v>
       </c>
       <c r="F13" t="n">
-        <v>1.559054796421383</v>
+        <v>1.510873878573771</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60.56208596683968</v>
       </c>
     </row>
     <row r="14">
@@ -1594,13 +1635,16 @@
         <v>15000000000</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07002004008016031</v>
+        <v>0.07099080694586313</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06989489211217831</v>
+        <v>0.07579928230215136</v>
       </c>
       <c r="F14" t="n">
-        <v>1.47657430287538</v>
+        <v>1.433907838828724</v>
+      </c>
+      <c r="G14" t="n">
+        <v>61.90958628417784</v>
       </c>
     </row>
     <row r="15">
@@ -1614,13 +1658,16 @@
         <v>16000000000</v>
       </c>
       <c r="D15" t="n">
-        <v>0.081062124248497</v>
+        <v>0.08130745658835546</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08046509080244568</v>
+        <v>0.08505989526124358</v>
       </c>
       <c r="F15" t="n">
-        <v>1.401949988163946</v>
+        <v>1.371819001361214</v>
+      </c>
+      <c r="G15" t="n">
+        <v>66.99015102215839</v>
       </c>
     </row>
     <row r="16">
@@ -1634,13 +1681,16 @@
         <v>17000000000</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08729458917835671</v>
+        <v>0.0898467824310521</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08726677802387195</v>
+        <v>0.08538216239905527</v>
       </c>
       <c r="F16" t="n">
-        <v>1.35777983279036</v>
+        <v>1.36975201769926</v>
+      </c>
+      <c r="G16" t="n">
+        <v>65.40736439755683</v>
       </c>
     </row>
     <row r="17">
@@ -1654,13 +1704,16 @@
         <v>18000000000</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09383767535070141</v>
+        <v>0.09730337078651685</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09392305471199353</v>
+        <v>0.09093224040590331</v>
       </c>
       <c r="F17" t="n">
-        <v>1.31697767061338</v>
+        <v>1.335036254908248</v>
+      </c>
+      <c r="G17" t="n">
+        <v>65.70185810685314</v>
       </c>
     </row>
     <row r="18">
@@ -1674,13 +1727,16 @@
         <v>19000000000</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0978056112224449</v>
+        <v>0.09818181818181818</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09884902208433932</v>
+        <v>0.1037423272687547</v>
       </c>
       <c r="F18" t="n">
-        <v>1.288137670669732</v>
+        <v>1.260512186419613</v>
+      </c>
+      <c r="G18" t="n">
+        <v>69.27688190272394</v>
       </c>
     </row>
     <row r="19">
@@ -1694,13 +1750,16 @@
         <v>20000000000</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1029959919839679</v>
+        <v>0.1090806945863126</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1027795442260118</v>
+        <v>0.09690173453756801</v>
       </c>
       <c r="F19" t="n">
-        <v>1.265871508321909</v>
+        <v>1.299409395313023</v>
+      </c>
+      <c r="G19" t="n">
+        <v>67.91583259982973</v>
       </c>
     </row>
     <row r="20">
@@ -1714,13 +1773,16 @@
         <v>3000000000</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1506112224448898</v>
+        <v>0.151144024514811</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1373785049536864</v>
+        <v>0.131498225329746</v>
       </c>
       <c r="F20" t="n">
-        <v>1.092173131506058</v>
+        <v>1.119336873415596</v>
+      </c>
+      <c r="G20" t="n">
+        <v>74.88923423093667</v>
       </c>
     </row>
     <row r="21">
@@ -1734,13 +1796,16 @@
         <v>4000000000</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05847695390781563</v>
+        <v>0.05945863125638406</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05811321294568711</v>
+        <v>0.05202779349646545</v>
       </c>
       <c r="F21" t="n">
-        <v>1.570811560934081</v>
+        <v>1.625502239720033</v>
+      </c>
+      <c r="G21" t="n">
+        <v>57.79890633739592</v>
       </c>
     </row>
     <row r="22">
@@ -1754,13 +1819,16 @@
         <v>5000000000</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006653306613226453</v>
+        <v>0.00602655771195097</v>
       </c>
       <c r="E22" t="n">
-        <v>0.006275240646548171</v>
+        <v>0.006361663276098057</v>
       </c>
       <c r="F22" t="n">
-        <v>2.496276266810687</v>
+        <v>2.491420980057189</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39.53527705718066</v>
       </c>
     </row>
     <row r="23">
@@ -1774,13 +1842,16 @@
         <v>6000000000</v>
       </c>
       <c r="D23" t="n">
-        <v>0.004949899799599198</v>
+        <v>0.005199182839632278</v>
       </c>
       <c r="E23" t="n">
-        <v>0.005130971820290084</v>
+        <v>0.005992119074657467</v>
       </c>
       <c r="F23" t="n">
-        <v>2.566875545465172</v>
+        <v>2.512608103587056</v>
+      </c>
+      <c r="G23" t="n">
+        <v>38.3060873807073</v>
       </c>
     </row>
     <row r="24">
@@ -1794,13 +1865,16 @@
         <v>7000000000</v>
       </c>
       <c r="D24" t="n">
-        <v>0.004398797595190381</v>
+        <v>0.004473953013278856</v>
       </c>
       <c r="E24" t="n">
-        <v>0.004614083012078167</v>
+        <v>0.005640047238611602</v>
       </c>
       <c r="F24" t="n">
-        <v>2.603483682909152</v>
+        <v>2.533899914081216</v>
+      </c>
+      <c r="G24" t="n">
+        <v>38.04805091213227</v>
       </c>
     </row>
     <row r="25">
@@ -1814,13 +1888,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.004248496993987976</v>
+        <v>0.004473953013278856</v>
       </c>
       <c r="E25" t="n">
-        <v>0.004534433477482991</v>
+        <v>0.004021343887681333</v>
       </c>
       <c r="F25" t="n">
-        <v>2.609447088742518</v>
+        <v>2.650272478199286</v>
+      </c>
+      <c r="G25" t="n">
+        <v>37.7625190664692</v>
       </c>
     </row>
     <row r="26">
@@ -1834,13 +1911,16 @@
         <v>9000000000</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005350701402805611</v>
+        <v>0.004902962206332993</v>
       </c>
       <c r="E26" t="n">
-        <v>0.005178002924062195</v>
+        <v>0.006150511738806047</v>
       </c>
       <c r="F26" t="n">
-        <v>2.563709911058256</v>
+        <v>2.503389070659998</v>
+      </c>
+      <c r="G26" t="n">
+        <v>38.80254022323701</v>
       </c>
     </row>
     <row r="27">
@@ -1854,13 +1934,16 @@
         <v>10000000000</v>
       </c>
       <c r="D27" t="n">
-        <v>0.006613226452905812</v>
+        <v>0.007201225740551583</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006799694476075809</v>
+        <v>0.007053041422213366</v>
       </c>
       <c r="F27" t="n">
-        <v>2.467674577753728</v>
+        <v>2.454550554700934</v>
+      </c>
+      <c r="G27" t="n">
+        <v>40.62872073340717</v>
       </c>
     </row>
     <row r="28">
@@ -1874,13 +1957,16 @@
         <v>11000000000</v>
       </c>
       <c r="D28" t="n">
-        <v>0.009729458917835672</v>
+        <v>0.01009193054136874</v>
       </c>
       <c r="E28" t="n">
-        <v>0.009941402806593801</v>
+        <v>0.01184643623892864</v>
       </c>
       <c r="F28" t="n">
-        <v>2.32855210988724</v>
+        <v>2.262073339481293</v>
+      </c>
+      <c r="G28" t="n">
+        <v>42.72024589651489</v>
       </c>
     </row>
     <row r="29">
@@ -1894,13 +1980,16 @@
         <v>12000000000</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01442885771543086</v>
+        <v>0.01437180796731359</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01436173204916564</v>
+        <v>0.01454806874632992</v>
       </c>
       <c r="F29" t="n">
-        <v>2.187261163843946</v>
+        <v>2.182181535376222</v>
+      </c>
+      <c r="G29" t="n">
+        <v>45.12478322198588</v>
       </c>
     </row>
     <row r="30">
@@ -1914,13 +2003,16 @@
         <v>13000000000</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01972945891783567</v>
+        <v>0.02042900919305414</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01958580433954494</v>
+        <v>0.0198455898670643</v>
       </c>
       <c r="F30" t="n">
-        <v>2.062379613418835</v>
+        <v>2.056948502610362</v>
+      </c>
+      <c r="G30" t="n">
+        <v>47.27872767219861</v>
       </c>
     </row>
     <row r="31">
@@ -1934,13 +2026,16 @@
         <v>14000000000</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02521042084168337</v>
+        <v>0.02602655771195097</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02558693555416958</v>
+        <v>0.02346103394487819</v>
       </c>
       <c r="F31" t="n">
-        <v>1.950018860536649</v>
+        <v>1.987002968473468</v>
+      </c>
+      <c r="G31" t="n">
+        <v>48.78783643774357</v>
       </c>
     </row>
     <row r="32">
@@ -1954,13 +2049,16 @@
         <v>15000000000</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03143286573146293</v>
+        <v>0.034341164453524</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03161215075255222</v>
+        <v>0.03098792174554416</v>
       </c>
       <c r="F32" t="n">
-        <v>1.857610815637918</v>
+        <v>1.8664685264371</v>
+      </c>
+      <c r="G32" t="n">
+        <v>51.16220869214131</v>
       </c>
     </row>
     <row r="33">
@@ -1974,13 +2072,16 @@
         <v>16000000000</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03935871743486974</v>
+        <v>0.03825331971399387</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03958635256378951</v>
+        <v>0.0405895729691619</v>
       </c>
       <c r="F33" t="n">
-        <v>1.755506527456893</v>
+        <v>1.743884993063779</v>
+      </c>
+      <c r="G33" t="n">
+        <v>53.30594288323821</v>
       </c>
     </row>
     <row r="34">
@@ -1994,13 +2095,16 @@
         <v>17000000000</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04481963927855712</v>
+        <v>0.04485188968335035</v>
       </c>
       <c r="E34" t="n">
-        <v>0.04414234735339474</v>
+        <v>0.0434726106118254</v>
       </c>
       <c r="F34" t="n">
-        <v>1.70451618638093</v>
+        <v>1.71173659599667</v>
+      </c>
+      <c r="G34" t="n">
+        <v>55.87652266139569</v>
       </c>
     </row>
     <row r="35">
@@ -2014,13 +2118,16 @@
         <v>18000000000</v>
       </c>
       <c r="D35" t="n">
-        <v>0.04763527054108217</v>
+        <v>0.05206332992849847</v>
       </c>
       <c r="E35" t="n">
-        <v>0.04797449545921203</v>
+        <v>0.04923994527551522</v>
       </c>
       <c r="F35" t="n">
-        <v>1.664818404661054</v>
+        <v>1.652268191825624</v>
+      </c>
+      <c r="G35" t="n">
+        <v>56.73870760550286</v>
       </c>
     </row>
     <row r="36">
@@ -2034,13 +2141,16 @@
         <v>19000000000</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0524248496993988</v>
+        <v>0.05263534218590398</v>
       </c>
       <c r="E36" t="n">
-        <v>0.05293522692003412</v>
+        <v>0.05111795446643045</v>
       </c>
       <c r="F36" t="n">
-        <v>1.617036261382865</v>
+        <v>1.634109269056932</v>
+      </c>
+      <c r="G36" t="n">
+        <v>58.36880800286239</v>
       </c>
     </row>
     <row r="37">
@@ -2054,13 +2164,16 @@
         <v>20000000000</v>
       </c>
       <c r="D37" t="n">
-        <v>0.05642284569138276</v>
+        <v>0.05661899897854954</v>
       </c>
       <c r="E37" t="n">
-        <v>0.05671294241850364</v>
+        <v>0.05252730692870886</v>
       </c>
       <c r="F37" t="n">
-        <v>1.582980606044597</v>
+        <v>1.620827617049345</v>
+      </c>
+      <c r="G37" t="n">
+        <v>56.93235313907721</v>
       </c>
     </row>
     <row r="38">
@@ -2074,13 +2187,16 @@
         <v>3000000000</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1434869739478958</v>
+        <v>0.1437997957099081</v>
       </c>
       <c r="E38" t="n">
-        <v>0.126658593070008</v>
+        <v>0.1278989323394006</v>
       </c>
       <c r="F38" t="n">
-        <v>1.142329253026652</v>
+        <v>1.136379277473381</v>
+      </c>
+      <c r="G38" t="n">
+        <v>75.69180071705136</v>
       </c>
     </row>
     <row r="39">
@@ -2094,13 +2210,16 @@
         <v>4000000000</v>
       </c>
       <c r="D39" t="n">
-        <v>0.04439879759519038</v>
+        <v>0.04598569969356486</v>
       </c>
       <c r="E39" t="n">
-        <v>0.04466278128376876</v>
+        <v>0.04771322002177263</v>
       </c>
       <c r="F39" t="n">
-        <v>1.698966145664418</v>
+        <v>1.667442544838207</v>
+      </c>
+      <c r="G39" t="n">
+        <v>55.47341284555506</v>
       </c>
     </row>
     <row r="40">
@@ -2114,13 +2233,16 @@
         <v>5000000000</v>
       </c>
       <c r="D40" t="n">
-        <v>0.001072144288577154</v>
+        <v>0.001103166496424923</v>
       </c>
       <c r="E40" t="n">
-        <v>0.001257889640506088</v>
+        <v>0.001326983693799491</v>
       </c>
       <c r="F40" t="n">
-        <v>3.02143707020643</v>
+        <v>3.00521092187308</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.16692721816969</v>
       </c>
     </row>
     <row r="41">
@@ -2134,13 +2256,16 @@
         <v>6000000000</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0007014028056112224</v>
+        <v>0.0007252298263534219</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0008218143398625444</v>
+        <v>0.0007264491358026414</v>
       </c>
       <c r="F41" t="n">
-        <v>3.148051259970502</v>
+        <v>3.183930628183133</v>
+      </c>
+      <c r="G41" t="n">
+        <v>32.34155498995634</v>
       </c>
     </row>
     <row r="42">
@@ -2154,13 +2279,16 @@
         <v>7000000000</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0006713426853707415</v>
+        <v>0.0006639427987742595</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0006988950158455922</v>
+        <v>0.0007426759537417556</v>
       </c>
       <c r="F42" t="n">
-        <v>3.195107009374795</v>
+        <v>3.177530256475567</v>
+      </c>
+      <c r="G42" t="n">
+        <v>31.40524907576679</v>
       </c>
     </row>
     <row r="43">
@@ -2174,13 +2302,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0005811623246492986</v>
+        <v>0.000449438202247191</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0006364919798427202</v>
+        <v>0.0004108320694709349</v>
       </c>
       <c r="F43" t="n">
-        <v>3.222001663691228</v>
+        <v>3.345391790507975</v>
+      </c>
+      <c r="G43" t="n">
+        <v>30.93443222359429</v>
       </c>
     </row>
     <row r="44">
@@ -2194,13 +2325,16 @@
         <v>9000000000</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0006913827655310621</v>
+        <v>0.0006639427987742595</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0007110856039240763</v>
+        <v>0.0007969803523931414</v>
       </c>
       <c r="F44" t="n">
-        <v>3.190113108310495</v>
+        <v>3.157009651373442</v>
+      </c>
+      <c r="G44" t="n">
+        <v>31.06475984797136</v>
       </c>
     </row>
     <row r="45">
@@ -2214,13 +2348,16 @@
         <v>10000000000</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0009919839679358717</v>
+        <v>0.001144024514811032</v>
       </c>
       <c r="E45" t="n">
-        <v>0.001007145957761331</v>
+        <v>0.001023146134446454</v>
       </c>
       <c r="F45" t="n">
-        <v>3.0881169389255</v>
+        <v>3.083430025670941</v>
+      </c>
+      <c r="G45" t="n">
+        <v>32.37019489992633</v>
       </c>
     </row>
     <row r="46">
@@ -2234,13 +2371,16 @@
         <v>11000000000</v>
       </c>
       <c r="D46" t="n">
-        <v>0.001753507014028056</v>
+        <v>0.001664964249233912</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001794366282231002</v>
+        <v>0.001702050234479784</v>
       </c>
       <c r="F46" t="n">
-        <v>2.912216975183715</v>
+        <v>2.928675092216945</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.01749719536738</v>
       </c>
     </row>
     <row r="47">
@@ -2254,13 +2394,16 @@
         <v>12000000000</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00343687374749499</v>
+        <v>0.003462717058222676</v>
       </c>
       <c r="E47" t="n">
-        <v>0.003314955631077081</v>
+        <v>0.002982788793449762</v>
       </c>
       <c r="F47" t="n">
-        <v>2.714883379895541</v>
+        <v>2.749667437799534</v>
+      </c>
+      <c r="G47" t="n">
+        <v>36.8020192573127</v>
       </c>
     </row>
     <row r="48">
@@ -2274,13 +2417,16 @@
         <v>13000000000</v>
       </c>
       <c r="D48" t="n">
-        <v>0.005060120240480962</v>
+        <v>0.004943820224719101</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005179827496190862</v>
+        <v>0.004592608430243535</v>
       </c>
       <c r="F48" t="n">
-        <v>2.56358761662416</v>
+        <v>2.605082393951514</v>
+      </c>
+      <c r="G48" t="n">
+        <v>38.55424436768901</v>
       </c>
     </row>
     <row r="49">
@@ -2294,13 +2440,16 @@
         <v>14000000000</v>
       </c>
       <c r="D49" t="n">
-        <v>0.007675350701402806</v>
+        <v>0.007170582226762002</v>
       </c>
       <c r="E49" t="n">
-        <v>0.007371627873486364</v>
+        <v>0.008207548117268749</v>
       </c>
       <c r="F49" t="n">
-        <v>2.438625073702119</v>
+        <v>2.399553157615405</v>
+      </c>
+      <c r="G49" t="n">
+        <v>40.97316941894533</v>
       </c>
     </row>
     <row r="50">
@@ -2314,13 +2463,16 @@
         <v>15000000000</v>
       </c>
       <c r="D50" t="n">
-        <v>0.009639278557114229</v>
+        <v>0.01074565883554648</v>
       </c>
       <c r="E50" t="n">
-        <v>0.009993489042578333</v>
+        <v>0.009290784815519891</v>
       </c>
       <c r="F50" t="n">
-        <v>2.326592237449534</v>
+        <v>2.353820738391537</v>
+      </c>
+      <c r="G50" t="n">
+        <v>42.34395490068501</v>
       </c>
     </row>
     <row r="51">
@@ -2334,13 +2486,16 @@
         <v>16000000000</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01384769539078156</v>
+        <v>0.01359550561797753</v>
       </c>
       <c r="E51" t="n">
-        <v>0.01349533251804028</v>
+        <v>0.01292953614654701</v>
       </c>
       <c r="F51" t="n">
-        <v>2.21165278735205</v>
+        <v>2.228321670051895</v>
+      </c>
+      <c r="G51" t="n">
+        <v>44.32242974904771</v>
       </c>
     </row>
     <row r="52">
@@ -2354,13 +2509,16 @@
         <v>17000000000</v>
       </c>
       <c r="D52" t="n">
-        <v>0.01644288577154309</v>
+        <v>0.01617977528089888</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01591793577677302</v>
+        <v>0.01704343387406472</v>
       </c>
       <c r="F52" t="n">
-        <v>2.146465335250082</v>
+        <v>2.119042590414823</v>
+      </c>
+      <c r="G52" t="n">
+        <v>46.03637540960334</v>
       </c>
     </row>
     <row r="53">
@@ -2374,13 +2532,16 @@
         <v>18000000000</v>
       </c>
       <c r="D53" t="n">
-        <v>0.01855711422845691</v>
+        <v>0.01905005107252298</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0183672557957241</v>
+        <v>0.01652517237316536</v>
       </c>
       <c r="F53" t="n">
-        <v>2.08870250100066</v>
+        <v>2.131471174288886</v>
+      </c>
+      <c r="G53" t="n">
+        <v>47.01547947449161</v>
       </c>
     </row>
     <row r="54">
@@ -2394,13 +2555,16 @@
         <v>19000000000</v>
       </c>
       <c r="D54" t="n">
-        <v>0.02061122244488978</v>
+        <v>0.0220020429009193</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02084262005713482</v>
+        <v>0.0215005945969282</v>
       </c>
       <c r="F54" t="n">
-        <v>2.036648886131846</v>
+        <v>2.023698440115609</v>
+      </c>
+      <c r="G54" t="n">
+        <v>47.28135207561039</v>
       </c>
     </row>
     <row r="55">
@@ -2414,13 +2578,16 @@
         <v>20000000000</v>
       </c>
       <c r="D55" t="n">
-        <v>0.02327655310621243</v>
+        <v>0.02431052093973442</v>
       </c>
       <c r="E55" t="n">
-        <v>0.02358779669789075</v>
+        <v>0.02131429781817599</v>
       </c>
       <c r="F55" t="n">
-        <v>1.984720350237774</v>
+        <v>2.027330780788382</v>
+      </c>
+      <c r="G55" t="n">
+        <v>48.61281453067902</v>
       </c>
     </row>
     <row r="56">
@@ -2434,13 +2601,16 @@
         <v>3000000000</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1402805611222445</v>
+        <v>0.1407252298263534</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1193038714594963</v>
+        <v>0.1281056315768049</v>
       </c>
       <c r="F56" t="n">
-        <v>1.178473871418411</v>
+        <v>1.135391634585087</v>
+      </c>
+      <c r="G56" t="n">
+        <v>75.90331924643442</v>
       </c>
     </row>
     <row r="57">
@@ -2454,13 +2624,16 @@
         <v>4000000000</v>
       </c>
       <c r="D57" t="n">
-        <v>0.03403807615230461</v>
+        <v>0.03420837589376916</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0350606368141474</v>
+        <v>0.03249855015016097</v>
       </c>
       <c r="F57" t="n">
-        <v>1.811126491479457</v>
+        <v>1.845278060303535</v>
+      </c>
+      <c r="G57" t="n">
+        <v>53.00867888375872</v>
       </c>
     </row>
     <row r="58">
@@ -2474,13 +2647,16 @@
         <v>5000000000</v>
       </c>
       <c r="D58" t="n">
-        <v>5.01002004008016e-05</v>
+        <v>9.193054136874361e-05</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0001399605337371456</v>
+        <v>0.0001878978530102791</v>
       </c>
       <c r="F58" t="n">
-        <v>3.63320626911482</v>
+        <v>3.556522921355439</v>
+      </c>
+      <c r="G58" t="n">
+        <v>27.98098881211306</v>
       </c>
     </row>
     <row r="59">
@@ -2494,13 +2670,16 @@
         <v>6000000000</v>
       </c>
       <c r="D59" t="n">
-        <v>4.008016032064128e-05</v>
+        <v>6.128702757916241e-05</v>
       </c>
       <c r="E59" t="n">
-        <v>8.792477441705028e-05</v>
+        <v>5.489435031227548e-05</v>
       </c>
       <c r="F59" t="n">
-        <v>3.751400486141542</v>
+        <v>3.867873254662345</v>
+      </c>
+      <c r="G59" t="n">
+        <v>26.7905521920158</v>
       </c>
     </row>
     <row r="60">
@@ -2514,13 +2693,16 @@
         <v>7000000000</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0001202404809619239</v>
+        <v>4.085801838610828e-05</v>
       </c>
       <c r="E60" t="n">
-        <v>5.207754286152354e-05</v>
+        <v>5.404644564473961e-05</v>
       </c>
       <c r="F60" t="n">
-        <v>3.880702726670798</v>
+        <v>3.871668507884304</v>
+      </c>
+      <c r="G60" t="n">
+        <v>25.82182887951311</v>
       </c>
     </row>
     <row r="61">
@@ -2534,13 +2716,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D61" t="n">
-        <v>2.004008016032064e-05</v>
+        <v>5.107252298263534e-05</v>
       </c>
       <c r="E61" t="n">
-        <v>3.553737446879437e-05</v>
+        <v>2.76596189538419e-05</v>
       </c>
       <c r="F61" t="n">
-        <v>3.972659045802415</v>
+        <v>4.031936066265674</v>
+      </c>
+      <c r="G61" t="n">
+        <v>25.2398633918724</v>
       </c>
     </row>
     <row r="62">
@@ -2554,13 +2739,16 @@
         <v>9000000000</v>
       </c>
       <c r="D62" t="n">
-        <v>5.01002004008016e-05</v>
+        <v>5.107252298263534e-05</v>
       </c>
       <c r="E62" t="n">
-        <v>3.186435833912881e-05</v>
+        <v>2.593228827783166e-05</v>
       </c>
       <c r="F62" t="n">
-        <v>3.998561151833527</v>
+        <v>4.047061687650689</v>
+      </c>
+      <c r="G62" t="n">
+        <v>25.11561663210321</v>
       </c>
     </row>
     <row r="63">
@@ -2574,13 +2762,16 @@
         <v>10000000000</v>
       </c>
       <c r="D63" t="n">
-        <v>4.008016032064128e-05</v>
+        <v>3.06435137895812e-05</v>
       </c>
       <c r="E63" t="n">
-        <v>6.007172420357439e-05</v>
+        <v>4.984233024930235e-05</v>
       </c>
       <c r="F63" t="n">
-        <v>3.845833256218361</v>
+        <v>3.89135815203037</v>
+      </c>
+      <c r="G63" t="n">
+        <v>25.86494090089963</v>
       </c>
     </row>
     <row r="64">
@@ -2594,13 +2785,16 @@
         <v>11000000000</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0001703406813627255</v>
+        <v>0.0001634320735444331</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0001460226514394126</v>
+        <v>0.0001537254029684721</v>
       </c>
       <c r="F64" t="n">
-        <v>3.62225563225109</v>
+        <v>3.608939912171382</v>
+      </c>
+      <c r="G64" t="n">
+        <v>27.22563594511788</v>
       </c>
     </row>
     <row r="65">
@@ -2614,13 +2808,16 @@
         <v>12000000000</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0003006012024048096</v>
+        <v>0.000296220633299285</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0003532704572551438</v>
+        <v>0.0003491129517392441</v>
       </c>
       <c r="F65" t="n">
-        <v>3.38702833019402</v>
+        <v>3.390274817731753</v>
+      </c>
+      <c r="G65" t="n">
+        <v>29.38231760261612</v>
       </c>
     </row>
     <row r="66">
@@ -2634,13 +2831,16 @@
         <v>13000000000</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0008416833667334669</v>
+        <v>0.0007354443309499489</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0007308607120379565</v>
+        <v>0.0006361702515423188</v>
       </c>
       <c r="F66" t="n">
-        <v>3.182177624129119</v>
+        <v>3.222146524215984</v>
+      </c>
+      <c r="G66" t="n">
+        <v>30.8215560722944</v>
       </c>
     </row>
     <row r="67">
@@ -2654,13 +2854,16 @@
         <v>14000000000</v>
       </c>
       <c r="D67" t="n">
-        <v>0.001092184368737475</v>
+        <v>0.00111338100102145</v>
       </c>
       <c r="E67" t="n">
-        <v>0.001203499243995236</v>
+        <v>0.001105125442100407</v>
       </c>
       <c r="F67" t="n">
-        <v>3.034794226836335</v>
+        <v>3.060422318476954</v>
+      </c>
+      <c r="G67" t="n">
+        <v>32.63739615139846</v>
       </c>
     </row>
     <row r="68">
@@ -2674,13 +2877,16 @@
         <v>15000000000</v>
       </c>
       <c r="D68" t="n">
-        <v>0.001663326653306613</v>
+        <v>0.001767109295199183</v>
       </c>
       <c r="E68" t="n">
-        <v>0.001740590898734585</v>
+        <v>0.002180652976815994</v>
       </c>
       <c r="F68" t="n">
-        <v>2.921707608900055</v>
+        <v>2.850773244646026</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.15512990400884</v>
       </c>
     </row>
     <row r="69">
@@ -2694,13 +2900,16 @@
         <v>16000000000</v>
       </c>
       <c r="D69" t="n">
-        <v>0.002444889779559118</v>
+        <v>0.002931562819203269</v>
       </c>
       <c r="E69" t="n">
-        <v>0.002727651410556268</v>
+        <v>0.003022391465771138</v>
       </c>
       <c r="F69" t="n">
-        <v>2.778842146173074</v>
+        <v>2.745342204334449</v>
+      </c>
+      <c r="G69" t="n">
+        <v>35.98070330521308</v>
       </c>
     </row>
     <row r="70">
@@ -2714,13 +2923,16 @@
         <v>17000000000</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00405811623246493</v>
+        <v>0.003667007150153217</v>
       </c>
       <c r="E70" t="n">
-        <v>0.003773813516727751</v>
+        <v>0.003292569411279978</v>
       </c>
       <c r="F70" t="n">
-        <v>2.671663602120086</v>
+        <v>2.717126727518734</v>
+      </c>
+      <c r="G70" t="n">
+        <v>37.50249515866815</v>
       </c>
     </row>
     <row r="71">
@@ -2734,13 +2946,16 @@
         <v>18000000000</v>
       </c>
       <c r="D71" t="n">
-        <v>0.004669338677354709</v>
+        <v>0.004300306435137896</v>
       </c>
       <c r="E71" t="n">
-        <v>0.004330445414897865</v>
+        <v>0.004342449920324561</v>
       </c>
       <c r="F71" t="n">
-        <v>2.625157445258012</v>
+        <v>2.624214782167702</v>
+      </c>
+      <c r="G71" t="n">
+        <v>38.09440736923416</v>
       </c>
     </row>
     <row r="72">
@@ -2754,13 +2969,16 @@
         <v>19000000000</v>
       </c>
       <c r="D72" t="n">
-        <v>0.004979959919839679</v>
+        <v>0.005628192032686415</v>
       </c>
       <c r="E72" t="n">
-        <v>0.005114120229277291</v>
+        <v>0.005823921080642596</v>
       </c>
       <c r="F72" t="n">
-        <v>2.56801610282557</v>
+        <v>2.522637444799797</v>
+      </c>
+      <c r="G72" t="n">
+        <v>38.80912600610886</v>
       </c>
     </row>
     <row r="73">
@@ -2774,13 +2992,16 @@
         <v>20000000000</v>
       </c>
       <c r="D73" t="n">
-        <v>0.006362725450901803</v>
+        <v>0.006496424923391216</v>
       </c>
       <c r="E73" t="n">
-        <v>0.006298474606782703</v>
+        <v>0.00568479966279251</v>
       </c>
       <c r="F73" t="n">
-        <v>2.494965176244447</v>
+        <v>2.531129097701731</v>
+      </c>
+      <c r="G73" t="n">
+        <v>39.97236001674999</v>
       </c>
     </row>
     <row r="74">
@@ -2794,13 +3015,16 @@
         <v>3000000000</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1409519038076152</v>
+        <v>0.1391930541368744</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1143832912589515</v>
+        <v>0.1283173429794531</v>
       </c>
       <c r="F74" t="n">
-        <v>1.20354217091473</v>
+        <v>1.134381189547472</v>
+      </c>
+      <c r="G74" t="n">
+        <v>76.48327363742973</v>
       </c>
     </row>
     <row r="75">
@@ -2814,13 +3038,16 @@
         <v>4000000000</v>
       </c>
       <c r="D75" t="n">
-        <v>0.02981963927855711</v>
+        <v>0.0289070480081716</v>
       </c>
       <c r="E75" t="n">
-        <v>0.03086483461452598</v>
+        <v>0.03772907629735293</v>
       </c>
       <c r="F75" t="n">
-        <v>1.86823250957262</v>
+        <v>1.777669495084999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>53.48441925461874</v>
       </c>
     </row>
     <row r="76">
@@ -2834,13 +3061,16 @@
         <v>5000000000</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>2.042900919305414e-05</v>
       </c>
       <c r="E76" t="n">
-        <v>1.213958844161315e-05</v>
+        <v>2.088641684382159e-05</v>
       </c>
       <c r="F76" t="n">
-        <v>4.221398042903426</v>
+        <v>4.097448903239137</v>
+      </c>
+      <c r="G76" t="n">
+        <v>23.767344122914</v>
       </c>
     </row>
     <row r="77">
@@ -2857,10 +3087,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>4.901123949630249e-06</v>
+        <v>3.351858998485403e-06</v>
       </c>
       <c r="F77" t="n">
-        <v>4.421490270511446</v>
+        <v>4.50288494529879</v>
+      </c>
+      <c r="G77" t="n">
+        <v>22.52139844014085</v>
       </c>
     </row>
     <row r="78">
@@ -2877,10 +3110,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>2.071105737260518e-06</v>
+        <v>1.118604435125586e-06</v>
       </c>
       <c r="F78" t="n">
-        <v>4.604116200401982</v>
+        <v>4.730723662694539</v>
+      </c>
+      <c r="G78" t="n">
+        <v>21.48558210867905</v>
       </c>
     </row>
     <row r="79">
@@ -2894,13 +3130,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1.021450459652707e-05</v>
       </c>
       <c r="E79" t="n">
-        <v>8.020444630736139e-07</v>
+        <v>1.206214906690048e-06</v>
       </c>
       <c r="F79" t="n">
-        <v>4.797811170132374</v>
+        <v>4.715394405846493</v>
+      </c>
+      <c r="G79" t="n">
+        <v>20.79273982389905</v>
       </c>
     </row>
     <row r="80">
@@ -2917,10 +3156,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>4.61734360804422e-07</v>
+        <v>8.287930646333158e-07</v>
       </c>
       <c r="F80" t="n">
-        <v>4.90728271581733</v>
+        <v>4.791234068853744</v>
+      </c>
+      <c r="G80" t="n">
+        <v>20.32547714553874</v>
       </c>
     </row>
     <row r="81">
@@ -2937,10 +3179,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.008644446218802e-06</v>
+        <v>9.994273393133733e-07</v>
       </c>
       <c r="F81" t="n">
-        <v>4.751684580115383</v>
+        <v>4.753540068673756</v>
+      </c>
+      <c r="G81" t="n">
+        <v>20.92690084178287</v>
       </c>
     </row>
     <row r="82">
@@ -2957,10 +3202,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3.571141899418026e-06</v>
+        <v>3.246268670459389e-06</v>
       </c>
       <c r="F82" t="n">
-        <v>4.489403666596851</v>
+        <v>4.509680368291113</v>
+      </c>
+      <c r="G82" t="n">
+        <v>22.35083347862285</v>
       </c>
     </row>
     <row r="83">
@@ -2974,13 +3222,16 @@
         <v>12000000000</v>
       </c>
       <c r="D83" t="n">
-        <v>2.004008016032064e-05</v>
+        <v>1.021450459652707e-05</v>
       </c>
       <c r="E83" t="n">
-        <v>1.4676634662062e-05</v>
+        <v>1.351665566430084e-05</v>
       </c>
       <c r="F83" t="n">
-        <v>4.178426601359396</v>
+        <v>4.197117988389776</v>
+      </c>
+      <c r="G83" t="n">
+        <v>23.92712512989127</v>
       </c>
     </row>
     <row r="84">
@@ -2994,13 +3245,16 @@
         <v>13000000000</v>
       </c>
       <c r="D84" t="n">
-        <v>4.008016032064128e-05</v>
+        <v>1.021450459652707e-05</v>
       </c>
       <c r="E84" t="n">
-        <v>4.204178720301908e-05</v>
+        <v>3.563654499502081e-05</v>
       </c>
       <c r="F84" t="n">
-        <v>3.932452567856672</v>
+        <v>3.971995421841723</v>
+      </c>
+      <c r="G84" t="n">
+        <v>25.31138012492719</v>
       </c>
     </row>
     <row r="85">
@@ -3014,13 +3268,16 @@
         <v>14000000000</v>
       </c>
       <c r="D85" t="n">
-        <v>4.008016032064128e-05</v>
+        <v>9.193054136874361e-05</v>
       </c>
       <c r="E85" t="n">
-        <v>8.265344208020253e-05</v>
+        <v>7.485232490228995e-05</v>
       </c>
       <c r="F85" t="n">
-        <v>3.766870209024009</v>
+        <v>3.7915588726557</v>
+      </c>
+      <c r="G85" t="n">
+        <v>26.32034999687509</v>
       </c>
     </row>
     <row r="86">
@@ -3034,13 +3291,16 @@
         <v>15000000000</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0001002004008016032</v>
+        <v>0.0001940755873340143</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0001248501102687728</v>
+        <v>0.0001011451772075338</v>
       </c>
       <c r="F86" t="n">
-        <v>3.662567198682697</v>
+        <v>3.716138961211338</v>
+      </c>
+      <c r="G86" t="n">
+        <v>27.51101657387541</v>
       </c>
     </row>
     <row r="87">
@@ -3054,13 +3314,16 @@
         <v>16000000000</v>
       </c>
       <c r="D87" t="n">
-        <v>0.000250501002004008</v>
+        <v>0.0002757916241062308</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0002366549266992577</v>
+        <v>0.0002314484918500071</v>
       </c>
       <c r="F87" t="n">
-        <v>3.495423644516711</v>
+        <v>3.501356038550621</v>
+      </c>
+      <c r="G87" t="n">
+        <v>28.72963595084271</v>
       </c>
     </row>
     <row r="88">
@@ -3074,13 +3337,16 @@
         <v>17000000000</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0004208416833667335</v>
+        <v>0.0004085801838610827</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0003732551362308146</v>
+        <v>0.0003290025091307761</v>
       </c>
       <c r="F88" t="n">
-        <v>3.371901921945332</v>
+        <v>3.406504350271798</v>
+      </c>
+      <c r="G88" t="n">
+        <v>29.86555488414178</v>
       </c>
     </row>
     <row r="89">
@@ -3094,13 +3360,16 @@
         <v>18000000000</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0005511022044088176</v>
+        <v>0.0006741573033707865</v>
       </c>
       <c r="E89" t="n">
-        <v>0.000504010731135933</v>
+        <v>0.0004542064692298899</v>
       </c>
       <c r="F89" t="n">
-        <v>3.288278285807732</v>
+        <v>3.317455780609178</v>
+      </c>
+      <c r="G89" t="n">
+        <v>30.63587391957167</v>
       </c>
     </row>
     <row r="90">
@@ -3114,13 +3383,16 @@
         <v>19000000000</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0007615230460921844</v>
+        <v>0.0007865168539325843</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0006461912656891775</v>
+        <v>0.0006328739663255278</v>
       </c>
       <c r="F90" t="n">
-        <v>3.217665920651415</v>
+        <v>3.223634609625768</v>
+      </c>
+      <c r="G90" t="n">
+        <v>30.78783895634959</v>
       </c>
     </row>
     <row r="91">
@@ -3134,13 +3406,16 @@
         <v>20000000000</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0007214428857715431</v>
+        <v>0.0008069458631256384</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0008299232258216617</v>
+        <v>0.0009673041464852779</v>
       </c>
       <c r="F91" t="n">
-        <v>3.145180043723908</v>
+        <v>3.100091559762938</v>
+      </c>
+      <c r="G91" t="n">
+        <v>31.99001711543697</v>
       </c>
     </row>
     <row r="92">
@@ -3154,13 +3429,16 @@
         <v>3000000000</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1373847695390782</v>
+        <v>0.1382022471910112</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1096431912529935</v>
+        <v>0.109696564557327</v>
       </c>
       <c r="F92" t="n">
-        <v>1.22842789268759</v>
+        <v>1.228143432851966</v>
+      </c>
+      <c r="G92" t="n">
+        <v>70.30247936247363</v>
       </c>
     </row>
     <row r="93">
@@ -3174,13 +3452,16 @@
         <v>4000000000</v>
       </c>
       <c r="D93" t="n">
-        <v>0.02455911823647295</v>
+        <v>0.02481103166496425</v>
       </c>
       <c r="E93" t="n">
-        <v>0.02652930485937397</v>
+        <v>0.02587557001534282</v>
       </c>
       <c r="F93" t="n">
-        <v>1.934443603710906</v>
+        <v>1.945198103408017</v>
+      </c>
+      <c r="G93" t="n">
+        <v>50.65694815805051</v>
       </c>
     </row>
     <row r="94">
@@ -3197,10 +3478,13 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>6.905704689641948e-07</v>
+        <v>8.713120370309115e-07</v>
       </c>
       <c r="F94" t="n">
-        <v>4.827707004583586</v>
+        <v>4.781187873750566</v>
+      </c>
+      <c r="G94" t="n">
+        <v>20.64014410899385</v>
       </c>
     </row>
     <row r="95">
@@ -3217,10 +3501,13 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1.816320709398885e-07</v>
+        <v>1.731202049341518e-07</v>
       </c>
       <c r="F95" t="n">
-        <v>5.087264969503228</v>
+        <v>5.096363279967837</v>
+      </c>
+      <c r="G95" t="n">
+        <v>19.62401560924889</v>
       </c>
     </row>
     <row r="96">
@@ -3237,10 +3524,13 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>3.535562032096236e-08</v>
+        <v>3.542819252679956e-08</v>
       </c>
       <c r="F96" t="n">
-        <v>5.389354400841778</v>
+        <v>5.388985846879967</v>
+      </c>
+      <c r="G96" t="n">
+        <v>18.52785489759058</v>
       </c>
     </row>
     <row r="97">
@@ -3257,10 +3547,13 @@
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>4.478921063893293e-09</v>
+        <v>6.815504777159823e-09</v>
       </c>
       <c r="F97" t="n">
-        <v>5.749366555994245</v>
+        <v>5.677960605903326</v>
+      </c>
+      <c r="G97" t="n">
+        <v>17.50611610985495</v>
       </c>
     </row>
     <row r="98">
@@ -3277,10 +3570,13 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>1.002899759276006e-09</v>
+        <v>2.190283540296539e-09</v>
       </c>
       <c r="F98" t="n">
-        <v>5.99733665924564</v>
+        <v>5.869141784841585</v>
+      </c>
+      <c r="G98" t="n">
+        <v>16.84949189386626</v>
       </c>
     </row>
     <row r="99">
@@ -3297,10 +3593,13 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>1.903122202448569e-09</v>
+        <v>1.66870103173597e-09</v>
       </c>
       <c r="F99" t="n">
-        <v>5.892400868085968</v>
+        <v>5.914077756865749</v>
+      </c>
+      <c r="G99" t="n">
+        <v>16.97690415198269</v>
       </c>
     </row>
     <row r="100">
@@ -3317,10 +3616,13 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>1.894618735070098e-08</v>
+        <v>2.842713297107659e-08</v>
       </c>
       <c r="F100" t="n">
-        <v>5.500403195872534</v>
+        <v>5.428422681203691</v>
+      </c>
+      <c r="G100" t="n">
+        <v>18.3773737287028</v>
       </c>
     </row>
     <row r="101">
@@ -3337,10 +3639,13 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>1.586921940413313e-07</v>
+        <v>6.705210445828647e-08</v>
       </c>
       <c r="F101" t="n">
-        <v>5.112820184776698</v>
+        <v>5.273146799667032</v>
+      </c>
+      <c r="G101" t="n">
+        <v>19.39489035795761</v>
       </c>
     </row>
     <row r="102">
@@ -3354,13 +3659,16 @@
         <v>13000000000</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1.021450459652707e-05</v>
       </c>
       <c r="E102" t="n">
-        <v>6.263214725478936e-07</v>
+        <v>7.216473464364527e-07</v>
       </c>
       <c r="F102" t="n">
-        <v>4.847123752685335</v>
+        <v>4.8189309790791</v>
+      </c>
+      <c r="G102" t="n">
+        <v>20.96460089235629</v>
       </c>
     </row>
     <row r="103">
@@ -3377,10 +3685,13 @@
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>1.714458578631631e-06</v>
+        <v>1.529215272748006e-06</v>
       </c>
       <c r="F103" t="n">
-        <v>4.643297704586019</v>
+        <v>4.666856309395235</v>
+      </c>
+      <c r="G103" t="n">
+        <v>21.47683456559434</v>
       </c>
     </row>
     <row r="104">
@@ -3397,10 +3708,13 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>2.405920988855223e-06</v>
+        <v>1.8437573732777e-06</v>
       </c>
       <c r="F104" t="n">
-        <v>4.57282840492768</v>
+        <v>4.628259666178107</v>
+      </c>
+      <c r="G104" t="n">
+        <v>21.81421101439383</v>
       </c>
     </row>
     <row r="105">
@@ -3417,10 +3731,13 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>6.057032097048592e-06</v>
+        <v>5.490464678291716e-06</v>
       </c>
       <c r="F105" t="n">
-        <v>4.375524845737634</v>
+        <v>4.396897251531144</v>
+      </c>
+      <c r="G105" t="n">
+        <v>23.4549036246383</v>
       </c>
     </row>
     <row r="106">
@@ -3434,13 +3751,16 @@
         <v>17000000000</v>
       </c>
       <c r="D106" t="n">
-        <v>1.002004008016032e-05</v>
+        <v>2.042900919305414e-05</v>
       </c>
       <c r="E106" t="n">
-        <v>1.213145579286243e-05</v>
+        <v>1.202249347061195e-05</v>
       </c>
       <c r="F106" t="n">
-        <v>4.221549074552573</v>
+        <v>4.223581961673388</v>
+      </c>
+      <c r="G106" t="n">
+        <v>24.07946877210142</v>
       </c>
     </row>
     <row r="107">
@@ -3454,13 +3774,16 @@
         <v>18000000000</v>
       </c>
       <c r="D107" t="n">
-        <v>1.002004008016032e-05</v>
+        <v>2.042900919305414e-05</v>
       </c>
       <c r="E107" t="n">
-        <v>1.945961373254111e-05</v>
+        <v>1.937128343356983e-05</v>
       </c>
       <c r="F107" t="n">
-        <v>4.113803790192337</v>
+        <v>4.114853338824919</v>
+      </c>
+      <c r="G107" t="n">
+        <v>24.62242254579153</v>
       </c>
     </row>
     <row r="108">
@@ -3474,13 +3797,16 @@
         <v>19000000000</v>
       </c>
       <c r="D108" t="n">
-        <v>6.012024048096193e-05</v>
+        <v>2.042900919305414e-05</v>
       </c>
       <c r="E108" t="n">
-        <v>2.769817638053698e-05</v>
+        <v>2.936534001711386e-05</v>
       </c>
       <c r="F108" t="n">
-        <v>4.03160875019062</v>
+        <v>4.017853541054799</v>
+      </c>
+      <c r="G108" t="n">
+        <v>25.4791246066905</v>
       </c>
     </row>
     <row r="109">
@@ -3494,13 +3820,16 @@
         <v>20000000000</v>
       </c>
       <c r="D109" t="n">
-        <v>4.008016032064128e-05</v>
+        <v>9.193054136874361e-05</v>
       </c>
       <c r="E109" t="n">
-        <v>4.523968910672033e-05</v>
+        <v>3.001145806161218e-05</v>
       </c>
       <c r="F109" t="n">
-        <v>3.914799460175106</v>
+        <v>4.01272070200452</v>
+      </c>
+      <c r="G109" t="n">
+        <v>25.30935970430965</v>
       </c>
     </row>
     <row r="110">
@@ -3514,13 +3843,16 @@
         <v>3000000000</v>
       </c>
       <c r="D110" t="n">
-        <v>0.1397695390781563</v>
+        <v>0.1396424923391215</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1097097820865341</v>
+        <v>0.1080408855925309</v>
       </c>
       <c r="F110" t="n">
-        <v>1.228073003694227</v>
+        <v>1.237014306988921</v>
+      </c>
+      <c r="G110" t="n">
+        <v>70.75140155946799</v>
       </c>
     </row>
     <row r="111">
@@ -3534,13 +3866,16 @@
         <v>4000000000</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0225250501002004</v>
+        <v>0.0221144024514811</v>
       </c>
       <c r="E111" t="n">
-        <v>0.02594045073261451</v>
+        <v>0.02328373860139231</v>
       </c>
       <c r="F111" t="n">
-        <v>1.944120667943022</v>
+        <v>1.990212996889179</v>
+      </c>
+      <c r="G111" t="n">
+        <v>49.92646206976975</v>
       </c>
     </row>
     <row r="112">
@@ -3557,10 +3892,13 @@
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>4.195021460163841e-08</v>
+        <v>4.592493897276474e-08</v>
       </c>
       <c r="F112" t="n">
-        <v>5.358532965999782</v>
+        <v>5.34215142256348</v>
+      </c>
+      <c r="G112" t="n">
+        <v>18.60982690309364</v>
       </c>
     </row>
     <row r="113">
@@ -3577,10 +3915,13 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>7.212131628396512e-09</v>
+        <v>7.068982189768869e-09</v>
       </c>
       <c r="F113" t="n">
-        <v>5.668274635537153</v>
+        <v>5.671709409995282</v>
+      </c>
+      <c r="G113" t="n">
+        <v>17.74210743762129</v>
       </c>
     </row>
     <row r="114">
@@ -3597,10 +3938,13 @@
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>4.488883277546774e-10</v>
+        <v>2.15417943969404e-10</v>
       </c>
       <c r="F114" t="n">
-        <v>6.126598448823749</v>
+        <v>6.242425904435927</v>
+      </c>
+      <c r="G114" t="n">
+        <v>16.47301826772377</v>
       </c>
     </row>
     <row r="115">
@@ -3617,10 +3961,13 @@
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>7.574460987190036e-12</v>
+        <v>1.167049814478609e-11</v>
       </c>
       <c r="F115" t="n">
-        <v>6.746466311575288</v>
+        <v>6.68343214389935</v>
+      </c>
+      <c r="G115" t="n">
+        <v>14.80404266002977</v>
       </c>
     </row>
     <row r="116">
@@ -3637,10 +3984,13 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>1.21775547334596e-13</v>
+        <v>2.106020053809596e-13</v>
       </c>
       <c r="F116" t="n">
-        <v>7.322413066348366</v>
+        <v>7.248567017427514</v>
+      </c>
+      <c r="G116" t="n">
+        <v>13.7380306636096</v>
       </c>
     </row>
     <row r="117">
@@ -3657,10 +4007,13 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>3.208185456198853e-13</v>
+        <v>1.139850760773669e-13</v>
       </c>
       <c r="F117" t="n">
-        <v>7.191328895050179</v>
+        <v>7.331276860192682</v>
+      </c>
+      <c r="G117" t="n">
+        <v>13.97519075016239</v>
       </c>
     </row>
     <row r="118">
@@ -3677,10 +4030,13 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>6.472444423898733e-12</v>
+        <v>1.378963456566072e-11</v>
       </c>
       <c r="F118" t="n">
-        <v>6.76925313043435</v>
+        <v>6.658948954975874</v>
+      </c>
+      <c r="G118" t="n">
+        <v>14.93776026147962</v>
       </c>
     </row>
     <row r="119">
@@ -3697,10 +4053,13 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>1.500143394854288e-10</v>
+        <v>3.33710755395994e-11</v>
       </c>
       <c r="F119" t="n">
-        <v>6.298763847062389</v>
+        <v>6.527801308557629</v>
+      </c>
+      <c r="G119" t="n">
+        <v>15.79700029387656</v>
       </c>
     </row>
     <row r="120">
@@ -3717,10 +4076,13 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>1.281912028084913e-09</v>
+        <v>7.496605000875745e-10</v>
       </c>
       <c r="F120" t="n">
-        <v>5.957336239798471</v>
+        <v>6.044437563670935</v>
+      </c>
+      <c r="G120" t="n">
+        <v>16.83578733346633</v>
       </c>
     </row>
     <row r="121">
@@ -3737,10 +4099,13 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>5.872238016728567e-09</v>
+        <v>1.823291675992766e-09</v>
       </c>
       <c r="F121" t="n">
-        <v>5.70339446990862</v>
+        <v>5.899475762797696</v>
+      </c>
+      <c r="G121" t="n">
+        <v>17.59939173892091</v>
       </c>
     </row>
     <row r="122">
@@ -3757,10 +4122,13 @@
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>6.031141994648435e-09</v>
+        <v>3.978279768936569e-09</v>
       </c>
       <c r="F122" t="n">
-        <v>5.698843571514229</v>
+        <v>5.76937600739528</v>
+      </c>
+      <c r="G122" t="n">
+        <v>17.60529337771033</v>
       </c>
     </row>
     <row r="123">
@@ -3777,10 +4145,13 @@
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>2.272271431135973e-08</v>
+        <v>2.356536640403503e-08</v>
       </c>
       <c r="F123" t="n">
-        <v>5.468268041696331</v>
+        <v>5.461808881042568</v>
+      </c>
+      <c r="G123" t="n">
+        <v>18.27874232125376</v>
       </c>
     </row>
     <row r="124">
@@ -3797,10 +4168,13 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>6.253649409365233e-08</v>
+        <v>7.414688834488397e-08</v>
       </c>
       <c r="F124" t="n">
-        <v>5.285922284451424</v>
+        <v>5.254665458818969</v>
+      </c>
+      <c r="G124" t="n">
+        <v>19.17584934534158</v>
       </c>
     </row>
     <row r="125">
@@ -3817,10 +4191,13 @@
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>1.32703546283212e-07</v>
+        <v>1.960068590423168e-07</v>
       </c>
       <c r="F125" t="n">
-        <v>5.146488948517598</v>
+        <v>5.072795497980761</v>
+      </c>
+      <c r="G125" t="n">
+        <v>19.54085749525792</v>
       </c>
     </row>
     <row r="126">
@@ -3837,10 +4214,13 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>2.325823851111088e-07</v>
+        <v>1.767885698600994e-07</v>
       </c>
       <c r="F126" t="n">
-        <v>5.040150962244589</v>
+        <v>5.092390384138369</v>
+      </c>
+      <c r="G126" t="n">
+        <v>19.76223771572004</v>
       </c>
     </row>
     <row r="127">
@@ -3857,10 +4237,13 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>4.340690046674473e-07</v>
+        <v>4.422641516619258e-07</v>
       </c>
       <c r="F127" t="n">
-        <v>4.919391215154316</v>
+        <v>4.915728681765919</v>
+      </c>
+      <c r="G127" t="n">
+        <v>20.63930672387119</v>
       </c>
     </row>
     <row r="128">
@@ -3874,13 +4257,16 @@
         <v>3000000000</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1401002004008016</v>
+        <v>0.1409703779366701</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1080284240575648</v>
+        <v>0.1093959895068737</v>
       </c>
       <c r="F128" t="n">
-        <v>1.237081443562297</v>
+        <v>1.229746684188547</v>
+      </c>
+      <c r="G128" t="n">
+        <v>70.95078470750128</v>
       </c>
     </row>
     <row r="129">
@@ -3894,13 +4280,16 @@
         <v>4000000000</v>
       </c>
       <c r="D129" t="n">
-        <v>0.02061122244488978</v>
+        <v>0.02119509703779367</v>
       </c>
       <c r="E129" t="n">
-        <v>0.02377038494700233</v>
+        <v>0.02398531229560135</v>
       </c>
       <c r="F129" t="n">
-        <v>1.981450547984921</v>
+        <v>1.977628562832363</v>
+      </c>
+      <c r="G129" t="n">
+        <v>49.66223421245913</v>
       </c>
     </row>
     <row r="130">
@@ -3917,10 +4306,13 @@
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>3.012173711864557e-09</v>
+        <v>2.393230674312153e-09</v>
       </c>
       <c r="F130" t="n">
-        <v>5.816080468908479</v>
+        <v>5.854430909849737</v>
+      </c>
+      <c r="G130" t="n">
+        <v>17.21914906243342</v>
       </c>
     </row>
     <row r="131">
@@ -3937,10 +4329,13 @@
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>3.179187433983823e-10</v>
+        <v>1.711984446962779e-10</v>
       </c>
       <c r="F131" t="n">
-        <v>6.181280436273908</v>
+        <v>6.278253702118816</v>
+      </c>
+      <c r="G131" t="n">
+        <v>16.15708200920513</v>
       </c>
     </row>
     <row r="132">
@@ -3957,10 +4352,13 @@
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>6.954081633063378e-12</v>
+        <v>4.033578155388579e-12</v>
       </c>
       <c r="F132" t="n">
-        <v>6.758860073094548</v>
+        <v>6.837349858393758</v>
+      </c>
+      <c r="G132" t="n">
+        <v>14.7202559554072</v>
       </c>
     </row>
     <row r="133">
@@ -3977,10 +4375,13 @@
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>2.102843884956879e-15</v>
+        <v>1.187296432576195e-15</v>
       </c>
       <c r="F133" t="n">
-        <v>7.84864124753391</v>
+        <v>7.920026855872704</v>
+      </c>
+      <c r="G133" t="n">
+        <v>12.74286305640959</v>
       </c>
     </row>
     <row r="134">
@@ -3997,10 +4398,13 @@
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>3.736896535912088e-19</v>
+        <v>4.175244328276489e-19</v>
       </c>
       <c r="F134" t="n">
-        <v>8.867601963641572</v>
+        <v>8.855238742079651</v>
+      </c>
+      <c r="G134" t="n">
+        <v>11.248608086716</v>
       </c>
     </row>
     <row r="135">
@@ -4017,10 +4421,13 @@
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>7.065525157988138e-19</v>
+        <v>1.24602942015773e-19</v>
       </c>
       <c r="F135" t="n">
-        <v>8.796372068883873</v>
+        <v>8.989125259311129</v>
+      </c>
+      <c r="G135" t="n">
+        <v>11.32742092523703</v>
       </c>
     </row>
     <row r="136">
@@ -4037,10 +4444,13 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>3.812137922396996e-17</v>
+        <v>4.477187509791279e-17</v>
       </c>
       <c r="F136" t="n">
-        <v>8.336932184752328</v>
+        <v>8.317889081321228</v>
+      </c>
+      <c r="G136" t="n">
+        <v>12.00536339652107</v>
       </c>
     </row>
     <row r="137">
@@ -4057,10 +4467,13 @@
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>6.749011618661573e-15</v>
+        <v>1.801964283960232e-15</v>
       </c>
       <c r="F137" t="n">
-        <v>7.701023905823043</v>
+        <v>7.867987056074055</v>
+      </c>
+      <c r="G137" t="n">
+        <v>13.01119200829604</v>
       </c>
     </row>
     <row r="138">
@@ -4077,10 +4490,13 @@
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>1.167437636007253e-13</v>
+        <v>1.052361553458172e-13</v>
       </c>
       <c r="F138" t="n">
-        <v>7.328071857323168</v>
+        <v>7.341970171099598</v>
+      </c>
+      <c r="G138" t="n">
+        <v>13.73294638875463</v>
       </c>
     </row>
     <row r="139">
@@ -4097,10 +4513,13 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>2.4113947301177e-12</v>
+        <v>9.537314363650281e-13</v>
       </c>
       <c r="F139" t="n">
-        <v>6.910696775119919</v>
+        <v>7.04108668381853</v>
+      </c>
+      <c r="G139" t="n">
+        <v>14.40657517837857</v>
       </c>
     </row>
     <row r="140">
@@ -4117,10 +4536,13 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>7.573197587857236e-13</v>
+        <v>8.179051571810286e-13</v>
       </c>
       <c r="F140" t="n">
-        <v>7.073142365712789</v>
+        <v>7.06245947478309</v>
+      </c>
+      <c r="G140" t="n">
+        <v>14.05344345140324</v>
       </c>
     </row>
     <row r="141">
@@ -4137,10 +4559,13 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>4.405779528776064e-12</v>
+        <v>2.477858525811379e-12</v>
       </c>
       <c r="F141" t="n">
-        <v>6.824689661122679</v>
+        <v>6.906839030257223</v>
+      </c>
+      <c r="G141" t="n">
+        <v>14.73599135432637</v>
       </c>
     </row>
     <row r="142">
@@ -4157,10 +4582,13 @@
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>2.638321270404687e-11</v>
+        <v>1.70021182168349e-11</v>
       </c>
       <c r="F142" t="n">
-        <v>6.562913598822311</v>
+        <v>6.628096844136272</v>
+      </c>
+      <c r="G142" t="n">
+        <v>15.33401702011975</v>
       </c>
     </row>
     <row r="143">
@@ -4177,10 +4605,13 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>8.5120474767966e-11</v>
+        <v>9.825805098204506e-11</v>
       </c>
       <c r="F143" t="n">
-        <v>6.386035991616175</v>
+        <v>6.3640390819385</v>
+      </c>
+      <c r="G143" t="n">
+        <v>15.52245229040321</v>
       </c>
     </row>
     <row r="144">
@@ -4197,10 +4628,13 @@
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>1.553199055576079e-10</v>
+        <v>2.074348658357593e-10</v>
       </c>
       <c r="F144" t="n">
-        <v>6.293373431174492</v>
+        <v>6.248328004645465</v>
+      </c>
+      <c r="G144" t="n">
+        <v>16.25444014733654</v>
       </c>
     </row>
     <row r="145">
@@ -4217,10 +4651,13 @@
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>4.292443069828343e-10</v>
+        <v>7.907041249495701e-10</v>
       </c>
       <c r="F145" t="n">
-        <v>6.133717590234783</v>
+        <v>6.035836997429732</v>
+      </c>
+      <c r="G145" t="n">
+        <v>16.5317186857789</v>
       </c>
     </row>
     <row r="146">
@@ -4234,13 +4671,16 @@
         <v>3000000000</v>
       </c>
       <c r="D146" t="n">
-        <v>0.1414729458917836</v>
+        <v>0.141144024514811</v>
       </c>
       <c r="E146" t="n">
-        <v>0.1079461573966036</v>
+        <v>0.1123477348479611</v>
       </c>
       <c r="F146" t="n">
-        <v>1.2375247955316</v>
+        <v>1.214136851673612</v>
+      </c>
+      <c r="G146" t="n">
+        <v>71.87519327449667</v>
       </c>
     </row>
     <row r="147">
@@ -4254,13 +4694,16 @@
         <v>4000000000</v>
       </c>
       <c r="D147" t="n">
-        <v>0.01935871743486974</v>
+        <v>0.02004085801838611</v>
       </c>
       <c r="E147" t="n">
-        <v>0.02329180864862683</v>
+        <v>0.02407810263385073</v>
       </c>
       <c r="F147" t="n">
-        <v>1.990066438206356</v>
+        <v>1.975987391296958</v>
+      </c>
+      <c r="G147" t="n">
+        <v>49.7743753909577</v>
       </c>
     </row>
     <row r="148">
@@ -4277,10 +4720,13 @@
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>3.164950321854485e-10</v>
+        <v>2.747411997792234e-10</v>
       </c>
       <c r="F148" t="n">
-        <v>6.181988828231559</v>
+        <v>6.20427896976341</v>
+      </c>
+      <c r="G148" t="n">
+        <v>16.26175634609271</v>
       </c>
     </row>
     <row r="149">
@@ -4297,10 +4743,13 @@
         <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>1.771031266600533e-11</v>
+        <v>5.866996658861068e-11</v>
       </c>
       <c r="F149" t="n">
-        <v>6.622068742227404</v>
+        <v>6.442734407417666</v>
+      </c>
+      <c r="G149" t="n">
+        <v>15.14455640479591</v>
       </c>
     </row>
     <row r="150">
@@ -4317,10 +4766,13 @@
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>1.238134481665608e-13</v>
+        <v>7.575410424777303e-13</v>
       </c>
       <c r="F150" t="n">
-        <v>7.320186320134332</v>
+        <v>7.073101841845595</v>
+      </c>
+      <c r="G150" t="n">
+        <v>13.69350596530568</v>
       </c>
     </row>
     <row r="151">
@@ -4337,10 +4789,13 @@
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>3.31538869013652e-19</v>
+        <v>8.600550337019611e-20</v>
       </c>
       <c r="F151" t="n">
-        <v>8.880923115631743</v>
+        <v>9.029783984020233</v>
+      </c>
+      <c r="G151" t="n">
+        <v>11.2464166299342</v>
       </c>
     </row>
     <row r="152">
@@ -4357,10 +4812,13 @@
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>6.116696773526347e-27</v>
+        <v>1.072422432562313e-27</v>
       </c>
       <c r="F152" t="n">
-        <v>10.68294064916957</v>
+        <v>10.84334414990579</v>
+      </c>
+      <c r="G152" t="n">
+        <v>9.362623802805187</v>
       </c>
     </row>
     <row r="153">
@@ -4377,10 +4835,13 @@
         <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>3.325265252638817e-27</v>
+        <v>1.980584765373867e-26</v>
       </c>
       <c r="F153" t="n">
-        <v>10.73935790551351</v>
+        <v>10.57334313627701</v>
+      </c>
+      <c r="G153" t="n">
+        <v>9.317032675409969</v>
       </c>
     </row>
     <row r="154">
@@ -4397,10 +4858,13 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>3.027557924977991e-24</v>
+        <v>7.510023270512396e-24</v>
       </c>
       <c r="F154" t="n">
-        <v>10.0909973158747</v>
+        <v>10.00143764698733</v>
+      </c>
+      <c r="G154" t="n">
+        <v>9.871066443645047</v>
       </c>
     </row>
     <row r="155">
@@ -4417,10 +4881,13 @@
         <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>4.016853948748333e-21</v>
+        <v>2.978593551775561e-21</v>
       </c>
       <c r="F155" t="n">
-        <v>9.35920738548791</v>
+        <v>9.390754677576531</v>
+      </c>
+      <c r="G155" t="n">
+        <v>10.73858346194608</v>
       </c>
     </row>
     <row r="156">
@@ -4437,10 +4904,13 @@
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>6.81289612127801e-20</v>
+        <v>9.762799047829138e-19</v>
       </c>
       <c r="F156" t="n">
-        <v>9.05524790105728</v>
+        <v>8.759996763597133</v>
+      </c>
+      <c r="G156" t="n">
+        <v>11.07753846799365</v>
       </c>
     </row>
     <row r="157">
@@ -4457,10 +4927,13 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>1.55316319955528e-17</v>
+        <v>3.248429148162966e-16</v>
       </c>
       <c r="F157" t="n">
-        <v>8.442495781055413</v>
+        <v>8.079620599562199</v>
+      </c>
+      <c r="G157" t="n">
+        <v>11.88370977015443</v>
       </c>
     </row>
     <row r="158">
@@ -4477,10 +4950,13 @@
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>1.129620453024259e-18</v>
+        <v>1.402819495620966e-18</v>
       </c>
       <c r="F158" t="n">
-        <v>8.743536879233831</v>
+        <v>8.719042641357177</v>
+      </c>
+      <c r="G158" t="n">
+        <v>11.45099913282111</v>
       </c>
     </row>
     <row r="159">
@@ -4497,10 +4973,13 @@
         <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>1.623881802521832e-17</v>
+        <v>8.550270433112651e-18</v>
       </c>
       <c r="F159" t="n">
-        <v>8.43729128551419</v>
+        <v>8.511968250018672</v>
+      </c>
+      <c r="G159" t="n">
+        <v>11.83617005087798</v>
       </c>
     </row>
     <row r="160">
@@ -4517,10 +4996,13 @@
         <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>1.191281144608124e-16</v>
+        <v>4.666594291957701e-17</v>
       </c>
       <c r="F160" t="n">
-        <v>8.201070256558706</v>
+        <v>8.312975382475576</v>
+      </c>
+      <c r="G160" t="n">
+        <v>12.31365294873754</v>
       </c>
     </row>
     <row r="161">
@@ -4537,10 +5019,13 @@
         <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>4.239522714222059e-16</v>
+        <v>2.903141702276218e-16</v>
       </c>
       <c r="F161" t="n">
-        <v>8.047083327376029</v>
+        <v>8.093314202244708</v>
+      </c>
+      <c r="G161" t="n">
+        <v>12.6039549867145</v>
       </c>
     </row>
     <row r="162">
@@ -4557,10 +5042,13 @@
         <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>2.048149302233962e-15</v>
+        <v>1.795920709916647e-15</v>
       </c>
       <c r="F162" t="n">
-        <v>7.851946310152977</v>
+        <v>7.868407443410203</v>
+      </c>
+      <c r="G162" t="n">
+        <v>12.91399551081601</v>
       </c>
     </row>
     <row r="163">
@@ -4577,10 +5065,13 @@
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>9.509869829562499e-15</v>
+        <v>2.556592401655749e-15</v>
       </c>
       <c r="F163" t="n">
-        <v>7.657087268912875</v>
+        <v>7.824095828500708</v>
+      </c>
+      <c r="G163" t="n">
+        <v>13.00489041011049</v>
       </c>
     </row>
     <row r="164">
@@ -4594,13 +5085,16 @@
         <v>3000000000</v>
       </c>
       <c r="D164" t="n">
-        <v>0.1415931863727455</v>
+        <v>0.1413074565883555</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1073443451277209</v>
+        <v>0.1147839873705476</v>
       </c>
       <c r="F164" t="n">
-        <v>1.24077551101415</v>
+        <v>1.201472481772557</v>
+      </c>
+      <c r="G164" t="n">
+        <v>72.79815903101368</v>
       </c>
     </row>
     <row r="165">
@@ -4614,13 +5108,16 @@
         <v>4000000000</v>
       </c>
       <c r="D165" t="n">
-        <v>0.01923847695390781</v>
+        <v>0.01896833503575077</v>
       </c>
       <c r="E165" t="n">
-        <v>0.02269031509838922</v>
+        <v>0.02763916732676159</v>
       </c>
       <c r="F165" t="n">
-        <v>2.001109134275143</v>
+        <v>1.916682068718506</v>
+      </c>
+      <c r="G165" t="n">
+        <v>50.26540432551387</v>
       </c>
     </row>
     <row r="166">
@@ -4637,10 +5134,13 @@
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>6.446106094459193e-11</v>
+        <v>7.044381496932848e-11</v>
       </c>
       <c r="F166" t="n">
-        <v>6.428437639038008</v>
+        <v>6.414929948575943</v>
+      </c>
+      <c r="G166" t="n">
+        <v>15.65042656383931</v>
       </c>
     </row>
     <row r="167">
@@ -4657,10 +5157,13 @@
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>2.512623208495128e-12</v>
+        <v>5.48394990596949e-12</v>
       </c>
       <c r="F167" t="n">
-        <v>6.904861407614346</v>
+        <v>6.79319233502654</v>
+      </c>
+      <c r="G167" t="n">
+        <v>14.49600718148698</v>
       </c>
     </row>
     <row r="168">
@@ -4677,10 +5180,13 @@
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>4.971751440659995e-15</v>
+        <v>7.716302755512013e-15</v>
       </c>
       <c r="F168" t="n">
-        <v>7.739976707891155</v>
+        <v>7.683892602485158</v>
+      </c>
+      <c r="G168" t="n">
+        <v>12.89787014950637</v>
       </c>
     </row>
     <row r="169">
@@ -4697,10 +5203,13 @@
         <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>9.219998480261752e-23</v>
+        <v>2.772601704995157e-23</v>
       </c>
       <c r="F169" t="n">
-        <v>9.750037594603546</v>
+        <v>9.871280691770119</v>
+      </c>
+      <c r="G169" t="n">
+        <v>10.20707558338302</v>
       </c>
     </row>
     <row r="170">
@@ -4717,10 +5226,13 @@
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>3.817919498916567e-36</v>
+        <v>1.469565194110855e-37</v>
       </c>
       <c r="F170" t="n">
-        <v>12.49820242022651</v>
+        <v>12.75459107252584</v>
+      </c>
+      <c r="G170" t="n">
+        <v>8.009084248922637</v>
       </c>
     </row>
     <row r="171">
@@ -4737,10 +5249,13 @@
         <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>2.64823353525143e-38</v>
+        <v>1.823556295515151e-37</v>
       </c>
       <c r="F171" t="n">
-        <v>12.88745243260362</v>
+        <v>12.73776112959549</v>
+      </c>
+      <c r="G171" t="n">
+        <v>7.767497350470941</v>
       </c>
     </row>
     <row r="172">
@@ -4757,10 +5272,13 @@
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>8.362531844699529e-34</v>
+        <v>2.760158412620769e-33</v>
       </c>
       <c r="F172" t="n">
-        <v>12.06220194716124</v>
+        <v>11.96347394458471</v>
+      </c>
+      <c r="G172" t="n">
+        <v>8.308993854246793</v>
       </c>
     </row>
     <row r="173">
@@ -4777,10 +5295,13 @@
         <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>1.981404319754517e-30</v>
+        <v>1.473383935717758e-31</v>
       </c>
       <c r="F173" t="n">
-        <v>11.40466918821338</v>
+        <v>11.62866299594736</v>
+      </c>
+      <c r="G173" t="n">
+        <v>8.756886331538656</v>
       </c>
     </row>
     <row r="174">
@@ -4797,10 +5318,13 @@
         <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>1.917715590950753e-28</v>
+        <v>3.346308265525299e-28</v>
       </c>
       <c r="F174" t="n">
-        <v>10.99966759201793</v>
+        <v>10.9493499648868</v>
+      </c>
+      <c r="G174" t="n">
+        <v>9.118297640823839</v>
       </c>
     </row>
     <row r="175">
@@ -4817,10 +5341,13 @@
         <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>3.351712274336836e-24</v>
+        <v>2.586910460188797e-24</v>
       </c>
       <c r="F175" t="n">
-        <v>10.08100889297332</v>
+        <v>10.10642433471033</v>
+      </c>
+      <c r="G175" t="n">
+        <v>9.934701807404581</v>
       </c>
     </row>
     <row r="176">
@@ -4837,10 +5364,13 @@
         <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>8.423244243865136e-27</v>
+        <v>2.705576798968381e-27</v>
       </c>
       <c r="F176" t="n">
-        <v>10.65320403337781</v>
+        <v>10.7583825829226</v>
+      </c>
+      <c r="G176" t="n">
+        <v>9.432464015619052</v>
       </c>
     </row>
     <row r="177">
@@ -4857,10 +5387,13 @@
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>6.326273210847549e-26</v>
+        <v>9.377232790119004e-25</v>
       </c>
       <c r="F177" t="n">
-        <v>10.46390913467726</v>
+        <v>10.20540109098729</v>
+      </c>
+      <c r="G177" t="n">
+        <v>9.849786019232218</v>
       </c>
     </row>
     <row r="178">
@@ -4877,10 +5410,13 @@
         <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>7.2802483878353e-25</v>
+        <v>7.783735786856019e-25</v>
       </c>
       <c r="F178" t="n">
-        <v>10.22994305743009</v>
+        <v>10.22346496405064</v>
+      </c>
+      <c r="G178" t="n">
+        <v>9.919842903142543</v>
       </c>
     </row>
     <row r="179">
@@ -4897,10 +5433,13 @@
         <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>6.380996151804545e-24</v>
+        <v>7.001529537324598e-24</v>
       </c>
       <c r="F179" t="n">
-        <v>10.01755581040271</v>
+        <v>10.00837719472592</v>
+      </c>
+      <c r="G179" t="n">
+        <v>9.989853515260776</v>
       </c>
     </row>
     <row r="180">
@@ -4917,10 +5456,13 @@
         <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>7.080548340773214e-23</v>
+        <v>1.031604875965223e-23</v>
       </c>
       <c r="F180" t="n">
-        <v>9.776804511794419</v>
+        <v>9.969955635478268</v>
+      </c>
+      <c r="G180" t="n">
+        <v>10.28730538923647</v>
       </c>
     </row>
     <row r="181">
@@ -4937,10 +5479,13 @@
         <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>5.832805961115677e-22</v>
+        <v>1.119227586119972e-22</v>
       </c>
       <c r="F181" t="n">
-        <v>9.56097177914784</v>
+        <v>9.730339088036086</v>
+      </c>
+      <c r="G181" t="n">
+        <v>10.59011314264692</v>
       </c>
     </row>
     <row r="182">
@@ -4954,13 +5499,16 @@
         <v>3000000000</v>
       </c>
       <c r="D182" t="n">
-        <v>0.1419238476953908</v>
+        <v>0.1421552604698672</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1070148201253192</v>
+        <v>0.1045351136739499</v>
       </c>
       <c r="F182" t="n">
-        <v>1.242561023455599</v>
+        <v>1.256126175226185</v>
+      </c>
+      <c r="G182" t="n">
+        <v>69.96524559527265</v>
       </c>
     </row>
     <row r="183">
@@ -4974,13 +5522,16 @@
         <v>4000000000</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01920841683366734</v>
+        <v>0.01968335035750766</v>
       </c>
       <c r="E183" t="n">
-        <v>0.02266604469800653</v>
+        <v>0.01951747665262023</v>
       </c>
       <c r="F183" t="n">
-        <v>2.001559863112988</v>
+        <v>2.063818236722845</v>
+      </c>
+      <c r="G183" t="n">
+        <v>48.27206516918991</v>
       </c>
     </row>
     <row r="184">
@@ -4997,10 +5548,13 @@
         <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>1.845149615566071e-11</v>
+        <v>1.802787818411428e-11</v>
       </c>
       <c r="F184" t="n">
-        <v>6.616007392108811</v>
+        <v>6.619441880949675</v>
+      </c>
+      <c r="G184" t="n">
+        <v>15.11532085187535</v>
       </c>
     </row>
     <row r="185">
@@ -5017,10 +5571,13 @@
         <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>5.2765408091049e-13</v>
+        <v>4.425290109784669e-13</v>
       </c>
       <c r="F185" t="n">
-        <v>7.123093970140889</v>
+        <v>7.147293053171976</v>
+      </c>
+      <c r="G185" t="n">
+        <v>14.12501604088386</v>
       </c>
     </row>
     <row r="186">
@@ -5037,10 +5594,13 @@
         <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>4.59534680781905e-16</v>
+        <v>1.721594912070161e-16</v>
       </c>
       <c r="F186" t="n">
-        <v>8.037210194814579</v>
+        <v>8.156694097710815</v>
+      </c>
+      <c r="G186" t="n">
+        <v>12.46757288281093</v>
       </c>
     </row>
     <row r="187">
@@ -5057,10 +5617,13 @@
         <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>4.722736100861297e-26</v>
+        <v>3.770230265139081e-26</v>
       </c>
       <c r="F187" t="n">
-        <v>10.49156109408453</v>
+        <v>10.51281981744951</v>
+      </c>
+      <c r="G187" t="n">
+        <v>9.525277924538024</v>
       </c>
     </row>
     <row r="188">
@@ -5077,10 +5640,13 @@
         <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>1.684949906971206e-46</v>
+        <v>6.163515106962471e-45</v>
       </c>
       <c r="F188" t="n">
-        <v>14.26991481901741</v>
+        <v>14.01666647969582</v>
+      </c>
+      <c r="G188" t="n">
+        <v>6.995385140076879</v>
       </c>
     </row>
     <row r="189">
@@ -5097,10 +5663,13 @@
         <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>1.854331036459808e-52</v>
+        <v>1.824880773208806e-53</v>
       </c>
       <c r="F189" t="n">
-        <v>15.19688046894785</v>
+        <v>15.34805310724886</v>
+      </c>
+      <c r="G189" t="n">
+        <v>6.620722241861811</v>
       </c>
     </row>
     <row r="190">
@@ -5117,10 +5686,13 @@
         <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>1.74940157007637e-45</v>
+        <v>4.488359398950252e-43</v>
       </c>
       <c r="F190" t="n">
-        <v>14.10578376436676</v>
+        <v>13.70893383853277</v>
+      </c>
+      <c r="G190" t="n">
+        <v>7.13702969722606</v>
       </c>
     </row>
     <row r="191">
@@ -5137,10 +5709,13 @@
         <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>1.036214243816836e-42</v>
+        <v>3.695405111289091e-42</v>
       </c>
       <c r="F191" t="n">
-        <v>13.6480887767209</v>
+        <v>13.5551032290761</v>
+      </c>
+      <c r="G191" t="n">
+        <v>7.322674521018753</v>
       </c>
     </row>
     <row r="192">
@@ -5157,10 +5732,13 @@
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>1.506499605771007e-39</v>
+        <v>7.773741240443339e-40</v>
       </c>
       <c r="F192" t="n">
-        <v>13.10673310917973</v>
+        <v>13.15682916967631</v>
+      </c>
+      <c r="G192" t="n">
+        <v>7.608878298251526</v>
       </c>
     </row>
     <row r="193">
@@ -5177,10 +5755,13 @@
         <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>7.509937821491302e-33</v>
+        <v>7.704579092790044e-34</v>
       </c>
       <c r="F193" t="n">
-        <v>11.88009378205091</v>
+        <v>12.06894797547826</v>
+      </c>
+      <c r="G193" t="n">
+        <v>8.410703279817367</v>
       </c>
     </row>
     <row r="194">
@@ -5197,10 +5778,13 @@
         <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>5.513063109728354e-38</v>
+        <v>4.362154458082758e-40</v>
       </c>
       <c r="F194" t="n">
-        <v>12.83077111095135</v>
+        <v>13.20042358745665</v>
+      </c>
+      <c r="G194" t="n">
+        <v>7.848841927740952</v>
       </c>
     </row>
     <row r="195">
@@ -5217,10 +5801,13 @@
         <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>2.814716772184253e-37</v>
+        <v>8.924386297380028e-38</v>
       </c>
       <c r="F195" t="n">
-        <v>12.7038451238101</v>
+        <v>12.79340132533198</v>
+      </c>
+      <c r="G195" t="n">
+        <v>7.89303175410404</v>
       </c>
     </row>
     <row r="196">
@@ -5237,10 +5824,13 @@
         <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>6.765230606165919e-37</v>
+        <v>9.768375116251479e-38</v>
       </c>
       <c r="F196" t="n">
-        <v>12.63505203566788</v>
+        <v>12.78637859035705</v>
+      </c>
+      <c r="G196" t="n">
+        <v>8.004054694293943</v>
       </c>
     </row>
     <row r="197">
@@ -5257,10 +5847,13 @@
         <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>5.548437157128524e-36</v>
+        <v>3.660890012206554e-35</v>
       </c>
       <c r="F197" t="n">
-        <v>12.46844619335386</v>
+        <v>12.31717118069122</v>
+      </c>
+      <c r="G197" t="n">
+        <v>8.052758348570595</v>
       </c>
     </row>
     <row r="198">
@@ -5277,10 +5870,13 @@
         <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>1.018828181039839e-34</v>
+        <v>1.795725812649437e-34</v>
       </c>
       <c r="F198" t="n">
-        <v>12.23433547297035</v>
+        <v>12.18822816010434</v>
+      </c>
+      <c r="G198" t="n">
+        <v>8.257000855779093</v>
       </c>
     </row>
     <row r="199">
@@ -5297,10 +5893,13 @@
         <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>3.769196932007014e-33</v>
+        <v>4.628192680532506e-33</v>
       </c>
       <c r="F199" t="n">
-        <v>11.93758081723791</v>
+        <v>11.92048881113101</v>
+      </c>
+      <c r="G199" t="n">
+        <v>8.445205174184942</v>
       </c>
     </row>
     <row r="200">
@@ -5314,13 +5913,16 @@
         <v>3000000000</v>
       </c>
       <c r="D200" t="n">
-        <v>0.1414228456913828</v>
+        <v>0.1412768130745659</v>
       </c>
       <c r="E200" t="n">
-        <v>0.106433009862214</v>
+        <v>0.1119747518889734</v>
       </c>
       <c r="F200" t="n">
-        <v>1.245723236876786</v>
+        <v>1.216092981691788</v>
+      </c>
+      <c r="G200" t="n">
+        <v>72.21543820118656</v>
       </c>
     </row>
     <row r="201">
@@ -5334,13 +5936,16 @@
         <v>4000000000</v>
       </c>
       <c r="D201" t="n">
-        <v>0.01838677354709419</v>
+        <v>0.01832482124616956</v>
       </c>
       <c r="E201" t="n">
-        <v>0.02240128183501904</v>
+        <v>0.02486748811009202</v>
       </c>
       <c r="F201" t="n">
-        <v>2.006503425326406</v>
+        <v>1.962236328614362</v>
+      </c>
+      <c r="G201" t="n">
+        <v>49.72937388631203</v>
       </c>
     </row>
     <row r="202">
@@ -5357,10 +5962,13 @@
         <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>8.710039405723849e-12</v>
+        <v>1.244276430593461e-11</v>
       </c>
       <c r="F202" t="n">
-        <v>6.726158515351088</v>
+        <v>6.674040267788468</v>
+      </c>
+      <c r="G202" t="n">
+        <v>14.93029330067731</v>
       </c>
     </row>
     <row r="203">
@@ -5377,10 +5985,13 @@
         <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>1.695466829425425e-13</v>
+        <v>3.943420790805097e-13</v>
       </c>
       <c r="F203" t="n">
-        <v>7.277885329281472</v>
+        <v>7.163107564874267</v>
+      </c>
+      <c r="G203" t="n">
+        <v>13.76700269529039</v>
       </c>
     </row>
     <row r="204">
@@ -5397,10 +6008,13 @@
         <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>8.543181464403855e-17</v>
+        <v>4.751755287293108e-17</v>
       </c>
       <c r="F204" t="n">
-        <v>8.240939490809849</v>
+        <v>8.310829855933893</v>
+      </c>
+      <c r="G204" t="n">
+        <v>12.09834891141397</v>
       </c>
     </row>
     <row r="205">
@@ -5417,10 +6031,13 @@
         <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>8.604941626833935e-29</v>
+        <v>1.586099043864961e-29</v>
       </c>
       <c r="F205" t="n">
-        <v>11.07170287099151</v>
+        <v>11.22221614182473</v>
+      </c>
+      <c r="G205" t="n">
+        <v>9.020782107650199</v>
       </c>
     </row>
     <row r="206">
@@ -5437,10 +6054,13 @@
         <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>3.521279493459014e-57</v>
+        <v>2.121155351126272e-55</v>
       </c>
       <c r="F206" t="n">
-        <v>15.89338002318719</v>
+        <v>15.63443346410511</v>
+      </c>
+      <c r="G206" t="n">
+        <v>6.286085407676491</v>
       </c>
     </row>
     <row r="207">
@@ -5457,10 +6077,13 @@
         <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>8.916491280690068e-69</v>
+        <v>6.141560912029934e-69</v>
       </c>
       <c r="F207" t="n">
-        <v>17.48752691684204</v>
+        <v>17.50876446339085</v>
+      </c>
+      <c r="G207" t="n">
+        <v>5.722502586818796</v>
       </c>
     </row>
     <row r="208">
@@ -5477,10 +6100,13 @@
         <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>5.027289841026501e-59</v>
+        <v>8.334412944912005e-62</v>
       </c>
       <c r="F208" t="n">
-        <v>16.15750733650389</v>
+        <v>16.54757296168181</v>
+      </c>
+      <c r="G208" t="n">
+        <v>6.183154659176854</v>
       </c>
     </row>
     <row r="209">
@@ -5497,10 +6123,13 @@
         <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>2.838914950342891e-58</v>
+        <v>6.522313980734541e-60</v>
       </c>
       <c r="F209" t="n">
-        <v>16.05042025176385</v>
+        <v>16.28294095547994</v>
+      </c>
+      <c r="G209" t="n">
+        <v>6.242980226025977</v>
       </c>
     </row>
     <row r="210">
@@ -5517,10 +6146,13 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>3.712207275121092e-54</v>
+        <v>4.579036291241471e-53</v>
       </c>
       <c r="F210" t="n">
-        <v>15.45103285944817</v>
+        <v>15.28824808770314</v>
+      </c>
+      <c r="G210" t="n">
+        <v>6.462771340352703</v>
       </c>
     </row>
     <row r="211">
@@ -5537,10 +6169,13 @@
         <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>2.37564610395642e-42</v>
+        <v>3.895817579266637e-44</v>
       </c>
       <c r="F211" t="n">
-        <v>13.58748480880366</v>
+        <v>13.88516903179298</v>
+      </c>
+      <c r="G211" t="n">
+        <v>7.332268859117002</v>
       </c>
     </row>
     <row r="212">
@@ -5557,10 +6192,13 @@
         <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>1.264774894649047e-52</v>
+        <v>1.381614142488902e-54</v>
       </c>
       <c r="F212" t="n">
-        <v>15.22193054569059</v>
+        <v>15.51460665648385</v>
+      </c>
+      <c r="G212" t="n">
+        <v>6.6192264477603</v>
       </c>
     </row>
     <row r="213">
@@ -5577,10 +6215,13 @@
         <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>3.961527520870495e-53</v>
+        <v>1.10243928024e-52</v>
       </c>
       <c r="F213" t="n">
-        <v>15.2976803509504</v>
+        <v>15.23091387110718</v>
+      </c>
+      <c r="G213" t="n">
+        <v>6.529755662767656</v>
       </c>
     </row>
     <row r="214">
@@ -5597,10 +6238,13 @@
         <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>3.930074091799453e-55</v>
+        <v>3.872635896869905e-57</v>
       </c>
       <c r="F214" t="n">
-        <v>15.59509899396636</v>
+        <v>15.88741801503769</v>
+      </c>
+      <c r="G214" t="n">
+        <v>6.476661197177155</v>
       </c>
     </row>
     <row r="215">
@@ -5617,10 +6261,13 @@
         <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>8.581162474848351e-54</v>
+        <v>1.100983286350659e-55</v>
       </c>
       <c r="F215" t="n">
-        <v>15.39693113748641</v>
+        <v>15.67615186288232</v>
+      </c>
+      <c r="G215" t="n">
+        <v>6.486089581438718</v>
       </c>
     </row>
     <row r="216">
@@ -5637,10 +6284,13 @@
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>2.496717309038775e-52</v>
+        <v>1.086076635362669e-56</v>
       </c>
       <c r="F216" t="n">
-        <v>15.17737845733423</v>
+        <v>15.82263304938791</v>
+      </c>
+      <c r="G216" t="n">
+        <v>6.659404408929332</v>
       </c>
     </row>
     <row r="217">
@@ -5657,10 +6307,13 @@
         <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>8.0752173790686e-51</v>
+        <v>7.229627837700678e-51</v>
       </c>
       <c r="F217" t="n">
-        <v>14.94758342444958</v>
+        <v>14.95494894814045</v>
+      </c>
+      <c r="G217" t="n">
+        <v>6.697674082655077</v>
       </c>
     </row>
   </sheetData>
@@ -5674,7 +6327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5708,6 +6361,11 @@
           <t>Q</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EVM</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5720,13 +6378,16 @@
         <v>1500000000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2810921843687375</v>
+        <v>0.2819937369519833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2664678742913271</v>
+        <v>0.2566710828208503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3710759033701471</v>
+        <v>0.4063897893871919</v>
+      </c>
+      <c r="G2" t="n">
+        <v>52.0630442932225</v>
       </c>
     </row>
     <row r="3">
@@ -5740,13 +6401,16 @@
         <v>2000000000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2101603206412826</v>
+        <v>0.207901878914405</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2248908544291441</v>
+        <v>0.2371584121725657</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5248191106283788</v>
+        <v>0.478320043693127</v>
+      </c>
+      <c r="G3" t="n">
+        <v>37.49212067461213</v>
       </c>
     </row>
     <row r="4">
@@ -5760,13 +6424,16 @@
         <v>2500000000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1327354709418838</v>
+        <v>0.1328183716075157</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1648860273015967</v>
+        <v>0.1650126114844708</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7727065442075916</v>
+        <v>0.7721364249002105</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29.89247100570662</v>
       </c>
     </row>
     <row r="5">
@@ -5780,13 +6447,16 @@
         <v>3000000000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1262825651302605</v>
+        <v>0.1244363256784969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1592094457406779</v>
+        <v>0.1571877346686528</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7985377044147843</v>
+        <v>0.8078667528584363</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29.90776076554883</v>
       </c>
     </row>
     <row r="6">
@@ -5800,13 +6470,16 @@
         <v>3500000000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1228657314629259</v>
+        <v>0.1238100208768267</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1563401000199064</v>
+        <v>0.1771146239325746</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8117990742114046</v>
+        <v>0.7187326471458408</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28.8401203948207</v>
       </c>
     </row>
     <row r="7">
@@ -5820,13 +6493,16 @@
         <v>4000000000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1244889779559118</v>
+        <v>0.1272338204592902</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1597484782651645</v>
+        <v>0.1614064099186999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7960620991989452</v>
+        <v>0.788478117938623</v>
+      </c>
+      <c r="G7" t="n">
+        <v>29.42603819202741</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +6516,16 @@
         <v>4500000000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1324448897795591</v>
+        <v>0.1350104384133612</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1704872419672539</v>
+        <v>0.1990828257827938</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7477140656113148</v>
+        <v>0.6266517542531477</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30.47358076701193</v>
       </c>
     </row>
     <row r="9">
@@ -5860,13 +6539,16 @@
         <v>5000000000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1428256513026052</v>
+        <v>0.1436638830897704</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1806073408587971</v>
+        <v>0.1946596021241115</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7037000718033644</v>
+        <v>0.6447452730907263</v>
+      </c>
+      <c r="G9" t="n">
+        <v>31.04517765357218</v>
       </c>
     </row>
     <row r="10">
@@ -5880,13 +6562,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1535671342685371</v>
+        <v>0.155</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1907117306365704</v>
+        <v>0.1956198485711884</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6610743792581215</v>
+        <v>0.6407995435740861</v>
+      </c>
+      <c r="G10" t="n">
+        <v>31.82535999920713</v>
       </c>
     </row>
     <row r="11">
@@ -5900,13 +6585,16 @@
         <v>6000000000</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1669338677354709</v>
+        <v>0.1675469728601253</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2068364010435181</v>
+        <v>0.2008437711752972</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5954185392410101</v>
+        <v>0.6195055151439939</v>
+      </c>
+      <c r="G11" t="n">
+        <v>32.53424768282937</v>
       </c>
     </row>
     <row r="12">
@@ -5920,13 +6608,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1790180360721443</v>
+        <v>0.1794780793319415</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2176811737875828</v>
+        <v>0.2075341430120126</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5526791541292596</v>
+        <v>0.5926365971629938</v>
+      </c>
+      <c r="G12" t="n">
+        <v>34.23980527462863</v>
       </c>
     </row>
     <row r="13">
@@ -5940,13 +6631,16 @@
         <v>7000000000</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1934168336673347</v>
+        <v>0.191356993736952</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2213830321079998</v>
+        <v>0.2157815542574325</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5383220192049303</v>
+        <v>0.5600908400812392</v>
+      </c>
+      <c r="G13" t="n">
+        <v>37.20754498276266</v>
       </c>
     </row>
     <row r="14">
@@ -5960,13 +6654,16 @@
         <v>7500000000</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2056513026052104</v>
+        <v>0.1974112734864301</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2274126945664944</v>
+        <v>0.2189084769393607</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5151705418262423</v>
+        <v>0.5479067430974682</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35.98824375486923</v>
       </c>
     </row>
     <row r="15">
@@ -5980,13 +6677,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.207685370741483</v>
+        <v>0.2077453027139875</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2270044966968247</v>
+        <v>0.2183125095953744</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5167290351314872</v>
+        <v>0.5502226175927981</v>
+      </c>
+      <c r="G15" t="n">
+        <v>36.2405472353129</v>
       </c>
     </row>
     <row r="16">
@@ -6000,13 +6700,16 @@
         <v>8500000000</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2099899799599198</v>
+        <v>0.2086116910229645</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2320994827432886</v>
+        <v>0.2282064912353288</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4973646147317275</v>
+        <v>0.5121434126713638</v>
+      </c>
+      <c r="G16" t="n">
+        <v>40.76718481850566</v>
       </c>
     </row>
     <row r="17">
@@ -6020,13 +6723,16 @@
         <v>9000000000</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2155110220440882</v>
+        <v>0.2254070981210856</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2345940995330524</v>
+        <v>0.2399702849913906</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4879514003825638</v>
+        <v>0.4678095928084185</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40.66334550353466</v>
       </c>
     </row>
     <row r="18">
@@ -6040,13 +6746,16 @@
         <v>9500000000</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2184569138276553</v>
+        <v>0.2313465553235908</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2346085140444852</v>
+        <v>0.2355480486122048</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4878971347510871</v>
+        <v>0.4843632010760084</v>
+      </c>
+      <c r="G18" t="n">
+        <v>42.81853337509173</v>
       </c>
     </row>
     <row r="19">
@@ -6060,13 +6769,16 @@
         <v>10000000000</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2222845691382765</v>
+        <v>0.235</v>
       </c>
       <c r="E19" t="n">
-        <v>0.240053437241104</v>
+        <v>0.2449576313258177</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4674995704948903</v>
+        <v>0.4492929397722977</v>
+      </c>
+      <c r="G19" t="n">
+        <v>42.8316314043407</v>
       </c>
     </row>
     <row r="20">
@@ -6080,13 +6792,16 @@
         <v>1500000000</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2750701402805611</v>
+        <v>0.2745615866388309</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2603995074464606</v>
+        <v>0.2630254281487139</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3928927635779097</v>
+        <v>0.3834297590565426</v>
+      </c>
+      <c r="G20" t="n">
+        <v>48.45936912608217</v>
       </c>
     </row>
     <row r="21">
@@ -6100,13 +6815,16 @@
         <v>2000000000</v>
       </c>
       <c r="D21" t="n">
-        <v>0.196623246492986</v>
+        <v>0.199258872651357</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2125981280247307</v>
+        <v>0.2244098672404352</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5725811269610281</v>
+        <v>0.5266649025167175</v>
+      </c>
+      <c r="G21" t="n">
+        <v>36.35288858440327</v>
       </c>
     </row>
     <row r="22">
@@ -6120,13 +6838,16 @@
         <v>2500000000</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1020741482965932</v>
+        <v>0.1017954070981211</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1301670625661539</v>
+        <v>0.1350303434828082</v>
       </c>
       <c r="F22" t="n">
-        <v>0.940205488911326</v>
+        <v>0.9152109143680014</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27.49227883310207</v>
       </c>
     </row>
     <row r="23">
@@ -6140,13 +6861,16 @@
         <v>3000000000</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08924849699398797</v>
+        <v>0.09244258872651356</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1185890847486715</v>
+        <v>0.1225695763791699</v>
       </c>
       <c r="F23" t="n">
-        <v>1.002219567259488</v>
+        <v>0.9804739876852135</v>
+      </c>
+      <c r="G23" t="n">
+        <v>27.10806061041816</v>
       </c>
     </row>
     <row r="24">
@@ -6160,13 +6884,16 @@
         <v>3500000000</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08686372745490982</v>
+        <v>0.08629436325678497</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1166156806790132</v>
+        <v>0.1150682558538732</v>
       </c>
       <c r="F24" t="n">
-        <v>1.013177996475219</v>
+        <v>1.02185679818973</v>
+      </c>
+      <c r="G24" t="n">
+        <v>26.4775952237953</v>
       </c>
     </row>
     <row r="25">
@@ -6180,13 +6907,16 @@
         <v>4000000000</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08841683366733467</v>
+        <v>0.08831941544885177</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1202131014439516</v>
+        <v>0.1194610367103518</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9932907777298202</v>
+        <v>0.9974157189907814</v>
+      </c>
+      <c r="G25" t="n">
+        <v>26.81912848737163</v>
       </c>
     </row>
     <row r="26">
@@ -6200,13 +6930,16 @@
         <v>4500000000</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09511022044088176</v>
+        <v>0.0941231732776618</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1279171501061279</v>
+        <v>0.1351852694127109</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9519695985403844</v>
+        <v>0.9144240835384877</v>
+      </c>
+      <c r="G26" t="n">
+        <v>27.24387636424139</v>
       </c>
     </row>
     <row r="27">
@@ -6220,13 +6953,16 @@
         <v>5000000000</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1036472945891784</v>
+        <v>0.1045615866388309</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1403834538780089</v>
+        <v>0.1426560699851672</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8883437422638971</v>
+        <v>0.8771297145803708</v>
+      </c>
+      <c r="G27" t="n">
+        <v>27.46529864629868</v>
       </c>
     </row>
     <row r="28">
@@ -6240,13 +6976,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1162925851703407</v>
+        <v>0.1162526096033403</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1551224216761903</v>
+        <v>0.1550863250478527</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8174701673234561</v>
+        <v>0.8176386811305189</v>
+      </c>
+      <c r="G28" t="n">
+        <v>27.99987227981756</v>
       </c>
     </row>
     <row r="29">
@@ -6260,13 +6999,16 @@
         <v>6000000000</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1277454909819639</v>
+        <v>0.1287369519832985</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1676963608669334</v>
+        <v>0.1678174154225646</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7601075573665835</v>
+        <v>0.7595675739166374</v>
+      </c>
+      <c r="G29" t="n">
+        <v>28.8811145530856</v>
       </c>
     </row>
     <row r="30">
@@ -6280,13 +7022,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1405310621242485</v>
+        <v>0.1394258872651357</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1802269696109968</v>
+        <v>0.1940280933666237</v>
       </c>
       <c r="F30" t="n">
-        <v>0.705329425843268</v>
+        <v>0.647345671522885</v>
+      </c>
+      <c r="G30" t="n">
+        <v>29.71116561964891</v>
       </c>
     </row>
     <row r="31">
@@ -6300,13 +7045,16 @@
         <v>7000000000</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1508517034068136</v>
+        <v>0.1482150313152401</v>
       </c>
       <c r="E31" t="n">
-        <v>0.187701596455284</v>
+        <v>0.192123155803554</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6736441288359918</v>
+        <v>0.655216433115032</v>
+      </c>
+      <c r="G31" t="n">
+        <v>30.55156148339257</v>
       </c>
     </row>
     <row r="32">
@@ -6320,13 +7068,16 @@
         <v>7500000000</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1620941883767535</v>
+        <v>0.1610438413361169</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1903989666770937</v>
+        <v>0.1971684087210755</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6623755365711895</v>
+        <v>0.6344573026321714</v>
+      </c>
+      <c r="G32" t="n">
+        <v>33.65672421835074</v>
       </c>
     </row>
     <row r="33">
@@ -6340,13 +7091,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1642885771543086</v>
+        <v>0.1652505219206681</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1924011464894123</v>
+        <v>0.1894985578853417</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6540653189580306</v>
+        <v>0.6661276889020324</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.32423879598048</v>
       </c>
     </row>
     <row r="34">
@@ -6360,13 +7114,16 @@
         <v>8500000000</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1665030060120241</v>
+        <v>0.1663987473903967</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1962712252202256</v>
+        <v>0.1981969102866517</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6381286563395743</v>
+        <v>0.6302590750240067</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.12795531842877</v>
       </c>
     </row>
     <row r="35">
@@ -6380,13 +7137,16 @@
         <v>9000000000</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1697595190380762</v>
+        <v>0.1700208768267223</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1974126156794798</v>
+        <v>0.2070814766233113</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6334594672616001</v>
+        <v>0.5944408831490892</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.10627429666654</v>
       </c>
     </row>
     <row r="36">
@@ -6400,13 +7160,16 @@
         <v>9500000000</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1764929859719439</v>
+        <v>0.1856680584551148</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2037599984548524</v>
+        <v>0.2255763642980765</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6077398992734364</v>
+        <v>0.5221915461966473</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.86083722668561</v>
       </c>
     </row>
     <row r="37">
@@ -6420,13 +7183,16 @@
         <v>10000000000</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1807815631262525</v>
+        <v>0.180615866388309</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2083372322364836</v>
+        <v>0.2103607760388431</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5894402947440202</v>
+        <v>0.5814131016715325</v>
+      </c>
+      <c r="G37" t="n">
+        <v>35.0885620800463</v>
       </c>
     </row>
     <row r="38">
@@ -6440,13 +7206,16 @@
         <v>1500000000</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2670941883767535</v>
+        <v>0.2660960334029228</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2605701525487334</v>
+        <v>0.2669635760329488</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3922767506258997</v>
+        <v>0.3693016854275985</v>
+      </c>
+      <c r="G38" t="n">
+        <v>50.14635824784145</v>
       </c>
     </row>
     <row r="39">
@@ -6460,13 +7229,16 @@
         <v>2000000000</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1852204408817635</v>
+        <v>0.1849895615866388</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2054163381516951</v>
+        <v>0.2098952630735436</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6010947172750164</v>
+        <v>0.5832564105369925</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.52086436276524</v>
       </c>
     </row>
     <row r="40">
@@ -6480,13 +7252,16 @@
         <v>2500000000</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0756813627254509</v>
+        <v>0.07478079331941545</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1010032897758083</v>
+        <v>0.1069738320022585</v>
       </c>
       <c r="F40" t="n">
-        <v>1.104578881529789</v>
+        <v>1.068569823857039</v>
+      </c>
+      <c r="G40" t="n">
+        <v>25.57722360727911</v>
       </c>
     </row>
     <row r="41">
@@ -6500,13 +7275,16 @@
         <v>3000000000</v>
       </c>
       <c r="D41" t="n">
-        <v>0.06055110220440882</v>
+        <v>0.06220250521920668</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0844468421957504</v>
+        <v>0.09280642372097496</v>
       </c>
       <c r="F41" t="n">
-        <v>1.212838482683818</v>
+        <v>1.156482639418431</v>
+      </c>
+      <c r="G41" t="n">
+        <v>24.95683982248763</v>
       </c>
     </row>
     <row r="42">
@@ -6520,13 +7298,16 @@
         <v>3500000000</v>
       </c>
       <c r="D42" t="n">
-        <v>0.05695390781563126</v>
+        <v>0.05551148225469728</v>
       </c>
       <c r="E42" t="n">
-        <v>0.07951318065526455</v>
+        <v>0.08079250967379085</v>
       </c>
       <c r="F42" t="n">
-        <v>1.247988828347433</v>
+        <v>1.238726794024715</v>
+      </c>
+      <c r="G42" t="n">
+        <v>24.5530671879999</v>
       </c>
     </row>
     <row r="43">
@@ -6540,13 +7321,16 @@
         <v>4000000000</v>
       </c>
       <c r="D43" t="n">
-        <v>0.05816633266533066</v>
+        <v>0.05820459290187891</v>
       </c>
       <c r="E43" t="n">
-        <v>0.08221908543988247</v>
+        <v>0.07944891077930723</v>
       </c>
       <c r="F43" t="n">
-        <v>1.22852248361789</v>
+        <v>1.248456956376284</v>
+      </c>
+      <c r="G43" t="n">
+        <v>24.60551004142465</v>
       </c>
     </row>
     <row r="44">
@@ -6560,13 +7344,16 @@
         <v>4500000000</v>
       </c>
       <c r="D44" t="n">
-        <v>0.06250501002004008</v>
+        <v>0.06065762004175365</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08855310747186977</v>
+        <v>0.08688264920099757</v>
       </c>
       <c r="F44" t="n">
-        <v>1.184685999771585</v>
+        <v>1.196024330488229</v>
+      </c>
+      <c r="G44" t="n">
+        <v>24.93834416115907</v>
       </c>
     </row>
     <row r="45">
@@ -6580,13 +7367,16 @@
         <v>5000000000</v>
       </c>
       <c r="D45" t="n">
-        <v>0.07087174348697395</v>
+        <v>0.06955114822546973</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1003901988441754</v>
+        <v>0.09681098897133822</v>
       </c>
       <c r="F45" t="n">
-        <v>1.108358090467964</v>
+        <v>1.130744519924755</v>
+      </c>
+      <c r="G45" t="n">
+        <v>25.38232927635384</v>
       </c>
     </row>
     <row r="46">
@@ -6600,13 +7390,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0812124248496994</v>
+        <v>0.08093945720250521</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1137062565226013</v>
+        <v>0.1157509037373946</v>
       </c>
       <c r="F46" t="n">
-        <v>1.029559822061387</v>
+        <v>1.018018684639705</v>
+      </c>
+      <c r="G46" t="n">
+        <v>26.02143057805597</v>
       </c>
     </row>
     <row r="47">
@@ -6620,13 +7413,16 @@
         <v>6000000000</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09367735470941883</v>
+        <v>0.09342379958246347</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1273099183708591</v>
+        <v>0.12026592969636</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9551672679450272</v>
+        <v>0.9930016592865457</v>
+      </c>
+      <c r="G47" t="n">
+        <v>26.93357092697252</v>
       </c>
     </row>
     <row r="48">
@@ -6640,13 +7436,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1033466933867735</v>
+        <v>0.1043110647181628</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1403090269759688</v>
+        <v>0.14420010627945</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8887128835099004</v>
+        <v>0.8695733320850443</v>
+      </c>
+      <c r="G48" t="n">
+        <v>26.965379344887</v>
       </c>
     </row>
     <row r="49">
@@ -6660,13 +7459,16 @@
         <v>7000000000</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1128557114228457</v>
+        <v>0.1113987473903967</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1487652146449419</v>
+        <v>0.1549844786910853</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8475165988819678</v>
+        <v>0.8181142667575039</v>
+      </c>
+      <c r="G49" t="n">
+        <v>28.00915934563773</v>
       </c>
     </row>
     <row r="50">
@@ -6680,13 +7482,16 @@
         <v>7500000000</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1214929859719439</v>
+        <v>0.1209290187891441</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1514818347664266</v>
+        <v>0.153214144743285</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8345847359254775</v>
+        <v>0.826410881796357</v>
+      </c>
+      <c r="G50" t="n">
+        <v>28.62419794471689</v>
       </c>
     </row>
     <row r="51">
@@ -6700,13 +7505,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1228156312625251</v>
+        <v>0.1246346555323591</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1535177810641539</v>
+        <v>0.1462591433847632</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8249838678617744</v>
+        <v>0.8595731475108284</v>
+      </c>
+      <c r="G51" t="n">
+        <v>29.04133003751105</v>
       </c>
     </row>
     <row r="52">
@@ -6720,13 +7528,16 @@
         <v>8500000000</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1266733466933868</v>
+        <v>0.126356993736952</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1607017828543507</v>
+        <v>0.1669632739758054</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7916957730100964</v>
+        <v>0.7633823594729365</v>
+      </c>
+      <c r="G52" t="n">
+        <v>28.44972155339159</v>
       </c>
     </row>
     <row r="53">
@@ -6740,13 +7551,16 @@
         <v>9000000000</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1309118236472946</v>
+        <v>0.1322964509394572</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1631403899504947</v>
+        <v>0.1590929801648322</v>
       </c>
       <c r="F53" t="n">
-        <v>0.780594479202131</v>
+        <v>0.7990732368419428</v>
+      </c>
+      <c r="G53" t="n">
+        <v>29.05807619388194</v>
       </c>
     </row>
     <row r="54">
@@ -6760,13 +7574,16 @@
         <v>9500000000</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1346693386773547</v>
+        <v>0.1328705636743215</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1673897711744552</v>
+        <v>0.1677873165945905</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7614761430055889</v>
+        <v>0.7597018139207472</v>
+      </c>
+      <c r="G54" t="n">
+        <v>29.78492060607232</v>
       </c>
     </row>
     <row r="55">
@@ -6780,13 +7597,16 @@
         <v>10000000000</v>
       </c>
       <c r="D55" t="n">
-        <v>0.139188376753507</v>
+        <v>0.1401774530271399</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1712998680323179</v>
+        <v>0.1775036322183109</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7441269969389386</v>
+        <v>0.7170503669455406</v>
+      </c>
+      <c r="G55" t="n">
+        <v>30.65375135019426</v>
       </c>
     </row>
     <row r="56">
@@ -6800,13 +7620,16 @@
         <v>1500000000</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2641683366733467</v>
+        <v>0.2626931106471816</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2537880430787271</v>
+        <v>0.268058956275652</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4168773590608019</v>
+        <v>0.3653852053204893</v>
+      </c>
+      <c r="G56" t="n">
+        <v>46.84024701926462</v>
       </c>
     </row>
     <row r="57">
@@ -6820,13 +7643,16 @@
         <v>2000000000</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1777555110220441</v>
+        <v>0.178455114822547</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1959826036750179</v>
+        <v>0.2049419704307398</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6393115495892083</v>
+        <v>0.6029951417606881</v>
+      </c>
+      <c r="G57" t="n">
+        <v>32.6288362151415</v>
       </c>
     </row>
     <row r="58">
@@ -6840,13 +7666,16 @@
         <v>2500000000</v>
       </c>
       <c r="D58" t="n">
-        <v>0.05265531062124248</v>
+        <v>0.05321503131524009</v>
       </c>
       <c r="E58" t="n">
-        <v>0.07106369868289757</v>
+        <v>0.07918279640707171</v>
       </c>
       <c r="F58" t="n">
-        <v>1.312050202244115</v>
+        <v>1.25039819465798</v>
+      </c>
+      <c r="G58" t="n">
+        <v>23.83467269836526</v>
       </c>
     </row>
     <row r="59">
@@ -6860,13 +7689,16 @@
         <v>3000000000</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0388877755511022</v>
+        <v>0.03916492693110647</v>
       </c>
       <c r="E59" t="n">
-        <v>0.05778079061331352</v>
+        <v>0.0521937285560392</v>
       </c>
       <c r="F59" t="n">
-        <v>1.425259826394046</v>
+        <v>1.478839275199894</v>
+      </c>
+      <c r="G59" t="n">
+        <v>23.13376506036402</v>
       </c>
     </row>
     <row r="60">
@@ -6880,13 +7712,16 @@
         <v>3500000000</v>
       </c>
       <c r="D60" t="n">
-        <v>0.03411823647294589</v>
+        <v>0.03391440501043842</v>
       </c>
       <c r="E60" t="n">
-        <v>0.05023310097882189</v>
+        <v>0.04542642700675844</v>
       </c>
       <c r="F60" t="n">
-        <v>1.49868667192294</v>
+        <v>1.550018237720813</v>
+      </c>
+      <c r="G60" t="n">
+        <v>22.69770106126541</v>
       </c>
     </row>
     <row r="61">
@@ -6900,13 +7735,16 @@
         <v>4000000000</v>
       </c>
       <c r="D61" t="n">
-        <v>0.03287575150300601</v>
+        <v>0.03295407098121086</v>
       </c>
       <c r="E61" t="n">
-        <v>0.04879136081265231</v>
+        <v>0.04972981756594529</v>
       </c>
       <c r="F61" t="n">
-        <v>1.513667091340177</v>
+        <v>1.503877750605821</v>
+      </c>
+      <c r="G61" t="n">
+        <v>22.50814069502227</v>
       </c>
     </row>
     <row r="62">
@@ -6920,13 +7758,16 @@
         <v>4500000000</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0348496993987976</v>
+        <v>0.035</v>
       </c>
       <c r="E62" t="n">
-        <v>0.05234436220905399</v>
+        <v>0.04864872025516363</v>
       </c>
       <c r="F62" t="n">
-        <v>1.477338338730703</v>
+        <v>1.515167778591717</v>
+      </c>
+      <c r="G62" t="n">
+        <v>22.76798315434523</v>
       </c>
     </row>
     <row r="63">
@@ -6940,13 +7781,16 @@
         <v>5000000000</v>
       </c>
       <c r="D63" t="n">
-        <v>0.04125250501002004</v>
+        <v>0.04245302713987474</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0620438903066443</v>
+        <v>0.05616551880597039</v>
       </c>
       <c r="F63" t="n">
-        <v>1.38697176016384</v>
+        <v>1.440327669110211</v>
+      </c>
+      <c r="G63" t="n">
+        <v>23.45065012051662</v>
       </c>
     </row>
     <row r="64">
@@ -6960,13 +7804,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D64" t="n">
-        <v>0.05</v>
+        <v>0.05137787056367432</v>
       </c>
       <c r="E64" t="n">
-        <v>0.07375074136393128</v>
+        <v>0.08086015659669298</v>
       </c>
       <c r="F64" t="n">
-        <v>1.291101039605687</v>
+        <v>1.238239999053796</v>
+      </c>
+      <c r="G64" t="n">
+        <v>24.00359271127514</v>
       </c>
     </row>
     <row r="65">
@@ -6980,13 +7827,16 @@
         <v>6000000000</v>
       </c>
       <c r="D65" t="n">
-        <v>0.06153306613226453</v>
+        <v>0.06294363256784968</v>
       </c>
       <c r="E65" t="n">
-        <v>0.08829645106115193</v>
+        <v>0.09458695968262061</v>
       </c>
       <c r="F65" t="n">
-        <v>1.186418161896381</v>
+        <v>1.144945118137948</v>
+      </c>
+      <c r="G65" t="n">
+        <v>24.57711143505301</v>
       </c>
     </row>
     <row r="66">
@@ -7000,13 +7850,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D66" t="n">
-        <v>0.07120240480961924</v>
+        <v>0.06829853862212944</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1017069387884841</v>
+        <v>0.1018193127081603</v>
       </c>
       <c r="F66" t="n">
-        <v>1.100260807025877</v>
+        <v>1.099573101223476</v>
+      </c>
+      <c r="G66" t="n">
+        <v>25.38434618870387</v>
       </c>
     </row>
     <row r="67">
@@ -7020,13 +7873,16 @@
         <v>7000000000</v>
       </c>
       <c r="D67" t="n">
-        <v>0.07729458917835672</v>
+        <v>0.07586638830897703</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1067288446687714</v>
+        <v>0.106807686616357</v>
       </c>
       <c r="F67" t="n">
-        <v>1.070020119883385</v>
+        <v>1.069553139381098</v>
+      </c>
+      <c r="G67" t="n">
+        <v>25.88543364780872</v>
       </c>
     </row>
     <row r="68">
@@ -7040,13 +7896,16 @@
         <v>7500000000</v>
       </c>
       <c r="D68" t="n">
-        <v>0.08095190380761523</v>
+        <v>0.0872964509394572</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1123526620831578</v>
+        <v>0.1106434306987698</v>
       </c>
       <c r="F68" t="n">
-        <v>1.037276318973484</v>
+        <v>1.047109347688943</v>
+      </c>
+      <c r="G68" t="n">
+        <v>26.20763630364118</v>
       </c>
     </row>
     <row r="69">
@@ -7060,13 +7919,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D69" t="n">
-        <v>0.08676352705410821</v>
+        <v>0.08576200417536535</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1138447640089024</v>
+        <v>0.1142317694202106</v>
       </c>
       <c r="F69" t="n">
-        <v>1.028773680341086</v>
+        <v>1.026580475045537</v>
+      </c>
+      <c r="G69" t="n">
+        <v>27.25771930500265</v>
       </c>
     </row>
     <row r="70">
@@ -7080,13 +7942,16 @@
         <v>8500000000</v>
       </c>
       <c r="D70" t="n">
-        <v>0.08788577154308617</v>
+        <v>0.09099164926931107</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1159066361223885</v>
+        <v>0.1195631319226703</v>
       </c>
       <c r="F70" t="n">
-        <v>1.017145195095048</v>
+        <v>0.9968547499178069</v>
+      </c>
+      <c r="G70" t="n">
+        <v>26.67661408112784</v>
       </c>
     </row>
     <row r="71">
@@ -7100,13 +7965,16 @@
         <v>9000000000</v>
       </c>
       <c r="D71" t="n">
-        <v>0.09307615230460922</v>
+        <v>0.09234864300626305</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1242119014862579</v>
+        <v>0.1312629210610735</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9716358573692309</v>
+        <v>0.9345224594369569</v>
+      </c>
+      <c r="G71" t="n">
+        <v>26.99991392793323</v>
       </c>
     </row>
     <row r="72">
@@ -7120,13 +7988,16 @@
         <v>9500000000</v>
       </c>
       <c r="D72" t="n">
-        <v>0.09710420841683366</v>
+        <v>0.09769311064718163</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1259493658389424</v>
+        <v>0.1232509906551248</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9623676146193102</v>
+        <v>0.9767977132034955</v>
+      </c>
+      <c r="G72" t="n">
+        <v>27.0933029116656</v>
       </c>
     </row>
     <row r="73">
@@ -7140,13 +8011,16 @@
         <v>10000000000</v>
       </c>
       <c r="D73" t="n">
-        <v>0.1002805611222445</v>
+        <v>0.1024112734864301</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1311400457100398</v>
+        <v>0.1401557898433602</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9351581769185535</v>
+        <v>0.8894732879700652</v>
+      </c>
+      <c r="G73" t="n">
+        <v>27.36109726196901</v>
       </c>
     </row>
     <row r="74">
@@ -7160,13 +8034,16 @@
         <v>1500000000</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2578957915831663</v>
+        <v>0.2581732776617954</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2495215721464845</v>
+        <v>0.2562892449372525</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4324823754029953</v>
+        <v>0.4077762023457593</v>
+      </c>
+      <c r="G74" t="n">
+        <v>40.71429857165442</v>
       </c>
     </row>
     <row r="75">
@@ -7180,13 +8057,16 @@
         <v>2000000000</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1704909819639279</v>
+        <v>0.1727035490605428</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1898586279600333</v>
+        <v>0.1848145684413956</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6646260948464212</v>
+        <v>0.6858006138499766</v>
+      </c>
+      <c r="G75" t="n">
+        <v>30.44505678365471</v>
       </c>
     </row>
     <row r="76">
@@ -7200,13 +8080,16 @@
         <v>2500000000</v>
       </c>
       <c r="D76" t="n">
-        <v>0.03865731462925852</v>
+        <v>0.03941544885177453</v>
       </c>
       <c r="E76" t="n">
-        <v>0.05213971027218654</v>
+        <v>0.05855223967200326</v>
       </c>
       <c r="F76" t="n">
-        <v>1.479378333968858</v>
+        <v>1.418176278180307</v>
+      </c>
+      <c r="G76" t="n">
+        <v>22.54114029293893</v>
       </c>
     </row>
     <row r="77">
@@ -7220,13 +8103,16 @@
         <v>3000000000</v>
       </c>
       <c r="D77" t="n">
-        <v>0.02412825651302605</v>
+        <v>0.02361169102296451</v>
       </c>
       <c r="E77" t="n">
-        <v>0.03539226020141421</v>
+        <v>0.03337709755841745</v>
       </c>
       <c r="F77" t="n">
-        <v>1.672735585490416</v>
+        <v>1.700666689552382</v>
+      </c>
+      <c r="G77" t="n">
+        <v>21.51776057547231</v>
       </c>
     </row>
     <row r="78">
@@ -7240,13 +8126,16 @@
         <v>3500000000</v>
       </c>
       <c r="D78" t="n">
-        <v>0.018687374749499</v>
+        <v>0.01849686847599165</v>
       </c>
       <c r="E78" t="n">
-        <v>0.02736596262382645</v>
+        <v>0.02636027594967165</v>
       </c>
       <c r="F78" t="n">
-        <v>1.792981386894797</v>
+        <v>1.810011078365257</v>
+      </c>
+      <c r="G78" t="n">
+        <v>20.94891339442577</v>
       </c>
     </row>
     <row r="79">
@@ -7260,13 +8149,16 @@
         <v>4000000000</v>
       </c>
       <c r="D79" t="n">
-        <v>0.01535070140280561</v>
+        <v>0.01579331941544885</v>
       </c>
       <c r="E79" t="n">
-        <v>0.02316421860909537</v>
+        <v>0.02496315501441835</v>
       </c>
       <c r="F79" t="n">
-        <v>1.867934153455429</v>
+        <v>1.83457683659773</v>
+      </c>
+      <c r="G79" t="n">
+        <v>20.63285379034749</v>
       </c>
     </row>
     <row r="80">
@@ -7280,13 +8172,16 @@
         <v>4500000000</v>
       </c>
       <c r="D80" t="n">
-        <v>0.01729458917835671</v>
+        <v>0.01693110647181629</v>
       </c>
       <c r="E80" t="n">
-        <v>0.02555795586163033</v>
+        <v>0.0247712575657761</v>
       </c>
       <c r="F80" t="n">
-        <v>1.823983617697077</v>
+        <v>1.838038808912228</v>
+      </c>
+      <c r="G80" t="n">
+        <v>20.8244181311506</v>
       </c>
     </row>
     <row r="81">
@@ -7300,13 +8195,16 @@
         <v>5000000000</v>
       </c>
       <c r="D81" t="n">
-        <v>0.02038076152304609</v>
+        <v>0.02115866388308977</v>
       </c>
       <c r="E81" t="n">
-        <v>0.03242194672904982</v>
+        <v>0.03755236327350572</v>
       </c>
       <c r="F81" t="n">
-        <v>1.714382367909296</v>
+        <v>1.644177053252426</v>
+      </c>
+      <c r="G81" t="n">
+        <v>21.38925991031165</v>
       </c>
     </row>
     <row r="82">
@@ -7320,13 +8218,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D82" t="n">
-        <v>0.02823647294589178</v>
+        <v>0.02903966597077244</v>
       </c>
       <c r="E82" t="n">
-        <v>0.04204367356203193</v>
+        <v>0.04345373857030128</v>
       </c>
       <c r="F82" t="n">
-        <v>1.588751695036989</v>
+        <v>1.572318795588582</v>
+      </c>
+      <c r="G82" t="n">
+        <v>22.35060558306249</v>
       </c>
     </row>
     <row r="83">
@@ -7340,13 +8241,16 @@
         <v>6000000000</v>
       </c>
       <c r="D83" t="n">
-        <v>0.03583166332665331</v>
+        <v>0.03692066805845511</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0543291868542479</v>
+        <v>0.06002445649908499</v>
       </c>
       <c r="F83" t="n">
-        <v>1.457864731421903</v>
+        <v>1.404852252651662</v>
+      </c>
+      <c r="G83" t="n">
+        <v>22.88573172425407</v>
       </c>
     </row>
     <row r="84">
@@ -7360,13 +8264,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D84" t="n">
-        <v>0.04173346693386774</v>
+        <v>0.04408141962421712</v>
       </c>
       <c r="E84" t="n">
-        <v>0.06209596872868989</v>
+        <v>0.06303871372533704</v>
       </c>
       <c r="F84" t="n">
-        <v>1.386516485484548</v>
+        <v>1.3783241291855</v>
+      </c>
+      <c r="G84" t="n">
+        <v>23.51346962526698</v>
       </c>
     </row>
     <row r="85">
@@ -7380,13 +8287,16 @@
         <v>7000000000</v>
       </c>
       <c r="D85" t="n">
-        <v>0.04641282565130261</v>
+        <v>0.05159707724425888</v>
       </c>
       <c r="E85" t="n">
-        <v>0.06844745433454469</v>
+        <v>0.07155374505155836</v>
       </c>
       <c r="F85" t="n">
-        <v>1.333016025321732</v>
+        <v>1.308186715467366</v>
+      </c>
+      <c r="G85" t="n">
+        <v>23.93205128841535</v>
       </c>
     </row>
     <row r="86">
@@ -7400,13 +8310,16 @@
         <v>7500000000</v>
       </c>
       <c r="D86" t="n">
-        <v>0.04991983967935872</v>
+        <v>0.05244258872651357</v>
       </c>
       <c r="E86" t="n">
-        <v>0.07341813097303709</v>
+        <v>0.07324056106103199</v>
       </c>
       <c r="F86" t="n">
-        <v>1.29366348723878</v>
+        <v>1.295034979851021</v>
+      </c>
+      <c r="G86" t="n">
+        <v>23.99234940306819</v>
       </c>
     </row>
     <row r="87">
@@ -7420,13 +8333,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D87" t="n">
-        <v>0.05506012024048096</v>
+        <v>0.06067849686847599</v>
       </c>
       <c r="E87" t="n">
-        <v>0.07658520573330327</v>
+        <v>0.08497457708080793</v>
       </c>
       <c r="F87" t="n">
-        <v>1.269599815160004</v>
+        <v>1.209166533448628</v>
+      </c>
+      <c r="G87" t="n">
+        <v>24.44970818374723</v>
       </c>
     </row>
     <row r="88">
@@ -7440,13 +8356,16 @@
         <v>8500000000</v>
       </c>
       <c r="D88" t="n">
-        <v>0.05727454909819639</v>
+        <v>0.05617954070981211</v>
       </c>
       <c r="E88" t="n">
-        <v>0.07828118225664982</v>
+        <v>0.0812791877316776</v>
       </c>
       <c r="F88" t="n">
-        <v>1.257010539034319</v>
+        <v>1.235231119483416</v>
+      </c>
+      <c r="G88" t="n">
+        <v>24.56175968922003</v>
       </c>
     </row>
     <row r="89">
@@ -7460,13 +8379,16 @@
         <v>9000000000</v>
       </c>
       <c r="D89" t="n">
-        <v>0.06041082164328657</v>
+        <v>0.0605741127348643</v>
       </c>
       <c r="E89" t="n">
-        <v>0.08455509657680373</v>
+        <v>0.0837295290829853</v>
       </c>
       <c r="F89" t="n">
-        <v>1.212083922142072</v>
+        <v>1.217855881606506</v>
+      </c>
+      <c r="G89" t="n">
+        <v>24.56814369965266</v>
       </c>
     </row>
     <row r="90">
@@ -7480,13 +8402,16 @@
         <v>9500000000</v>
       </c>
       <c r="D90" t="n">
-        <v>0.06318637274549098</v>
+        <v>0.06315240083507306</v>
       </c>
       <c r="E90" t="n">
-        <v>0.08785948015577247</v>
+        <v>0.0804716175996492</v>
       </c>
       <c r="F90" t="n">
-        <v>1.189375475285815</v>
+        <v>1.241039979254471</v>
+      </c>
+      <c r="G90" t="n">
+        <v>24.78138224634503</v>
       </c>
     </row>
     <row r="91">
@@ -7500,13 +8425,16 @@
         <v>10000000000</v>
       </c>
       <c r="D91" t="n">
-        <v>0.06756513026052104</v>
+        <v>0.06701461377870564</v>
       </c>
       <c r="E91" t="n">
-        <v>0.09242397235530847</v>
+        <v>0.0969677636959234</v>
       </c>
       <c r="F91" t="n">
-        <v>1.158981008678251</v>
+        <v>1.129752085334123</v>
+      </c>
+      <c r="G91" t="n">
+        <v>25.34479832774153</v>
       </c>
     </row>
     <row r="92">
@@ -7520,13 +8448,16 @@
         <v>1500000000</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2536573146292585</v>
+        <v>0.2549895615866388</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2476606124860934</v>
+        <v>0.2647396890699593</v>
       </c>
       <c r="F92" t="n">
-        <v>0.4393219109357541</v>
+        <v>0.3772706192325662</v>
+      </c>
+      <c r="G92" t="n">
+        <v>44.36992758128548</v>
       </c>
     </row>
     <row r="93">
@@ -7540,13 +8471,16 @@
         <v>2000000000</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1679959919839679</v>
+        <v>0.1677557411273486</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1866744872231908</v>
+        <v>0.1931340895013355</v>
       </c>
       <c r="F93" t="n">
-        <v>0.6779575125783033</v>
+        <v>0.651034465709827</v>
+      </c>
+      <c r="G93" t="n">
+        <v>31.61578896080901</v>
       </c>
     </row>
     <row r="94">
@@ -7560,13 +8494,16 @@
         <v>2500000000</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0263627254509018</v>
+        <v>0.02633611691022964</v>
       </c>
       <c r="E94" t="n">
-        <v>0.03727705320758451</v>
+        <v>0.0411276754628187</v>
       </c>
       <c r="F94" t="n">
-        <v>1.647742731830023</v>
+        <v>1.599661031034615</v>
+      </c>
+      <c r="G94" t="n">
+        <v>21.55424079442374</v>
       </c>
     </row>
     <row r="95">
@@ -7580,13 +8517,16 @@
         <v>3000000000</v>
       </c>
       <c r="D95" t="n">
-        <v>0.01456913827655311</v>
+        <v>0.01434237995824635</v>
       </c>
       <c r="E95" t="n">
-        <v>0.02138475904587449</v>
+        <v>0.01874615753521617</v>
       </c>
       <c r="F95" t="n">
-        <v>1.903111297327927</v>
+        <v>1.960051651927035</v>
+      </c>
+      <c r="G95" t="n">
+        <v>20.04990791518421</v>
       </c>
     </row>
     <row r="96">
@@ -7600,13 +8540,16 @@
         <v>3500000000</v>
       </c>
       <c r="D96" t="n">
-        <v>0.008416833667334669</v>
+        <v>0.008684759916492693</v>
       </c>
       <c r="E96" t="n">
-        <v>0.01295574698404399</v>
+        <v>0.01439951149586554</v>
       </c>
       <c r="F96" t="n">
-        <v>2.113609209420706</v>
+        <v>2.070573216024003</v>
+      </c>
+      <c r="G96" t="n">
+        <v>19.26736853483215</v>
       </c>
     </row>
     <row r="97">
@@ -7620,13 +8563,16 @@
         <v>4000000000</v>
       </c>
       <c r="D97" t="n">
-        <v>0.006162324649298597</v>
+        <v>0.006085594989561587</v>
       </c>
       <c r="E97" t="n">
-        <v>0.009088576242401777</v>
+        <v>0.009061865100175939</v>
       </c>
       <c r="F97" t="n">
-        <v>2.253364065769781</v>
+        <v>2.254496134107179</v>
+      </c>
+      <c r="G97" t="n">
+        <v>18.78773090838958</v>
       </c>
     </row>
     <row r="98">
@@ -7640,13 +8586,16 @@
         <v>4500000000</v>
       </c>
       <c r="D98" t="n">
-        <v>0.005831663326653307</v>
+        <v>0.00581419624217119</v>
       </c>
       <c r="E98" t="n">
-        <v>0.008692871674670966</v>
+        <v>0.00966225956586712</v>
       </c>
       <c r="F98" t="n">
-        <v>2.270438493995781</v>
+        <v>2.229720177152361</v>
+      </c>
+      <c r="G98" t="n">
+        <v>18.81553036804423</v>
       </c>
     </row>
     <row r="99">
@@ -7660,13 +8609,16 @@
         <v>5000000000</v>
       </c>
       <c r="D99" t="n">
-        <v>0.007755511022044088</v>
+        <v>0.008173277661795406</v>
       </c>
       <c r="E99" t="n">
-        <v>0.01246374169598166</v>
+        <v>0.01354945250264772</v>
       </c>
       <c r="F99" t="n">
-        <v>2.129212967441322</v>
+        <v>2.095440265030192</v>
+      </c>
+      <c r="G99" t="n">
+        <v>19.53240211198417</v>
       </c>
     </row>
     <row r="100">
@@ -7680,13 +8632,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D100" t="n">
-        <v>0.01312625250501002</v>
+        <v>0.01273486430062631</v>
       </c>
       <c r="E100" t="n">
-        <v>0.01967610244822909</v>
+        <v>0.01612230580729088</v>
       </c>
       <c r="F100" t="n">
-        <v>1.939260660438467</v>
+        <v>2.023779780946261</v>
+      </c>
+      <c r="G100" t="n">
+        <v>20.43817156386897</v>
       </c>
     </row>
     <row r="101">
@@ -7700,13 +8655,16 @@
         <v>6000000000</v>
       </c>
       <c r="D101" t="n">
-        <v>0.01751503006012024</v>
+        <v>0.01735908141962422</v>
       </c>
       <c r="E101" t="n">
-        <v>0.02645722915664451</v>
+        <v>0.02631088211284414</v>
       </c>
       <c r="F101" t="n">
-        <v>1.808346357699816</v>
+        <v>1.810861120252821</v>
+      </c>
+      <c r="G101" t="n">
+        <v>20.98510340024536</v>
       </c>
     </row>
     <row r="102">
@@ -7720,13 +8678,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D102" t="n">
-        <v>0.02182364729458918</v>
+        <v>0.02080375782881002</v>
       </c>
       <c r="E102" t="n">
-        <v>0.03218404447155303</v>
+        <v>0.03382838199702216</v>
       </c>
       <c r="F102" t="n">
-        <v>1.717849233785391</v>
+        <v>1.694296166554677</v>
+      </c>
+      <c r="G102" t="n">
+        <v>21.42996736766223</v>
       </c>
     </row>
     <row r="103">
@@ -7740,13 +8701,16 @@
         <v>7000000000</v>
       </c>
       <c r="D103" t="n">
-        <v>0.02492985971943888</v>
+        <v>0.02427974947807933</v>
       </c>
       <c r="E103" t="n">
-        <v>0.03734991854026976</v>
+        <v>0.03444445280600702</v>
       </c>
       <c r="F103" t="n">
-        <v>1.646796977814986</v>
+        <v>1.685708939739069</v>
+      </c>
+      <c r="G103" t="n">
+        <v>21.60306887511157</v>
       </c>
     </row>
     <row r="104">
@@ -7760,13 +8724,16 @@
         <v>7500000000</v>
       </c>
       <c r="D104" t="n">
-        <v>0.02822645290581162</v>
+        <v>0.02834029227557411</v>
       </c>
       <c r="E104" t="n">
-        <v>0.04242881062647998</v>
+        <v>0.04113131287527363</v>
       </c>
       <c r="F104" t="n">
-        <v>1.584220740774069</v>
+        <v>1.599617332440678</v>
+      </c>
+      <c r="G104" t="n">
+        <v>22.03984017195872</v>
       </c>
     </row>
     <row r="105">
@@ -7780,13 +8747,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D105" t="n">
-        <v>0.02840681362725451</v>
+        <v>0.0291544885177453</v>
       </c>
       <c r="E105" t="n">
-        <v>0.04329215533770755</v>
+        <v>0.04470081850970409</v>
       </c>
       <c r="F105" t="n">
-        <v>1.574180407348205</v>
+        <v>1.558131062077942</v>
+      </c>
+      <c r="G105" t="n">
+        <v>22.11344084739096</v>
       </c>
     </row>
     <row r="106">
@@ -7800,13 +8770,16 @@
         <v>8500000000</v>
       </c>
       <c r="D106" t="n">
-        <v>0.03094188376753507</v>
+        <v>0.03028183716075157</v>
       </c>
       <c r="E106" t="n">
-        <v>0.04597337705711643</v>
+        <v>0.04329370144320259</v>
       </c>
       <c r="F106" t="n">
-        <v>1.54396970414417</v>
+        <v>1.57416256869328</v>
+      </c>
+      <c r="G106" t="n">
+        <v>22.33860193538457</v>
       </c>
     </row>
     <row r="107">
@@ -7820,13 +8793,16 @@
         <v>9000000000</v>
       </c>
       <c r="D107" t="n">
-        <v>0.03292585170340681</v>
+        <v>0.0329749478079332</v>
       </c>
       <c r="E107" t="n">
-        <v>0.04850919119363565</v>
+        <v>0.05357609368731454</v>
       </c>
       <c r="F107" t="n">
-        <v>1.516639039344544</v>
+        <v>1.46518818141259</v>
+      </c>
+      <c r="G107" t="n">
+        <v>22.43934801717515</v>
       </c>
     </row>
     <row r="108">
@@ -7840,13 +8816,16 @@
         <v>9500000000</v>
       </c>
       <c r="D108" t="n">
-        <v>0.03737474949899799</v>
+        <v>0.03588726513569938</v>
       </c>
       <c r="E108" t="n">
-        <v>0.05337919514064068</v>
+        <v>0.05605424637002529</v>
       </c>
       <c r="F108" t="n">
-        <v>1.467115933651518</v>
+        <v>1.44137775831833</v>
+      </c>
+      <c r="G108" t="n">
+        <v>22.6531805083864</v>
       </c>
     </row>
     <row r="109">
@@ -7860,13 +8839,16 @@
         <v>10000000000</v>
       </c>
       <c r="D109" t="n">
-        <v>0.03703406813627255</v>
+        <v>0.03790187891440501</v>
       </c>
       <c r="E109" t="n">
-        <v>0.05572375034021776</v>
+        <v>0.0589018812246123</v>
       </c>
       <c r="F109" t="n">
-        <v>1.444506091181473</v>
+        <v>1.414989129541887</v>
+      </c>
+      <c r="G109" t="n">
+        <v>22.8456575566131</v>
       </c>
     </row>
     <row r="110">
@@ -7880,13 +8862,16 @@
         <v>1500000000</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2529659318637275</v>
+        <v>0.2534237995824635</v>
       </c>
       <c r="E110" t="n">
-        <v>0.252472144286454</v>
+        <v>0.2517913601128841</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4216793878794751</v>
+        <v>0.4241675466771059</v>
+      </c>
+      <c r="G110" t="n">
+        <v>44.86655976028841</v>
       </c>
     </row>
     <row r="111">
@@ -7900,13 +8885,16 @@
         <v>2000000000</v>
       </c>
       <c r="D111" t="n">
-        <v>0.1674649298597194</v>
+        <v>0.1661377870563674</v>
       </c>
       <c r="E111" t="n">
-        <v>0.1888960644863978</v>
+        <v>0.185872391336282</v>
       </c>
       <c r="F111" t="n">
-        <v>0.6686436226064503</v>
+        <v>0.6813347335349921</v>
+      </c>
+      <c r="G111" t="n">
+        <v>31.49898350537165</v>
       </c>
     </row>
     <row r="112">
@@ -7920,13 +8908,16 @@
         <v>2500000000</v>
       </c>
       <c r="D112" t="n">
-        <v>0.0194188376753507</v>
+        <v>0.01989561586638831</v>
       </c>
       <c r="E112" t="n">
-        <v>0.02975147412467508</v>
+        <v>0.02527980131167158</v>
       </c>
       <c r="F112" t="n">
-        <v>1.7545444269725</v>
+        <v>1.828911925024419</v>
+      </c>
+      <c r="G112" t="n">
+        <v>20.98209611835399</v>
       </c>
     </row>
     <row r="113">
@@ -7940,13 +8931,16 @@
         <v>3000000000</v>
       </c>
       <c r="D113" t="n">
-        <v>0.008236472945891783</v>
+        <v>0.008475991649269311</v>
       </c>
       <c r="E113" t="n">
-        <v>0.01259394017038581</v>
+        <v>0.01677369664843978</v>
       </c>
       <c r="F113" t="n">
-        <v>2.12503322716851</v>
+        <v>2.007186037780161</v>
+      </c>
+      <c r="G113" t="n">
+        <v>18.99584651811704</v>
       </c>
     </row>
     <row r="114">
@@ -7960,13 +8954,16 @@
         <v>3500000000</v>
       </c>
       <c r="D114" t="n">
-        <v>0.003877755511022044</v>
+        <v>0.003862212943632568</v>
       </c>
       <c r="E114" t="n">
-        <v>0.005898047815111319</v>
+        <v>0.005671916266117729</v>
       </c>
       <c r="F114" t="n">
-        <v>2.415163970076291</v>
+        <v>2.429369471881007</v>
+      </c>
+      <c r="G114" t="n">
+        <v>17.79301344556031</v>
       </c>
     </row>
     <row r="115">
@@ -7980,13 +8977,16 @@
         <v>4000000000</v>
       </c>
       <c r="D115" t="n">
-        <v>0.001663326653306613</v>
+        <v>0.001784968684759917</v>
       </c>
       <c r="E115" t="n">
-        <v>0.002819784163133321</v>
+        <v>0.003306069319723927</v>
       </c>
       <c r="F115" t="n">
-        <v>2.672919713998841</v>
+        <v>2.619100969185966</v>
+      </c>
+      <c r="G115" t="n">
+        <v>17.2420713876894</v>
       </c>
     </row>
     <row r="116">
@@ -8000,13 +9000,16 @@
         <v>4500000000</v>
       </c>
       <c r="D116" t="n">
-        <v>0.001402805611222445</v>
+        <v>0.001544885177453027</v>
       </c>
       <c r="E116" t="n">
-        <v>0.00231191732357611</v>
+        <v>0.001875078259370719</v>
       </c>
       <c r="F116" t="n">
-        <v>2.738867957876059</v>
+        <v>2.807020323518171</v>
+      </c>
+      <c r="G116" t="n">
+        <v>17.26984914140557</v>
       </c>
     </row>
     <row r="117">
@@ -8020,13 +9023,16 @@
         <v>5000000000</v>
       </c>
       <c r="D117" t="n">
-        <v>0.001943887775551102</v>
+        <v>0.002150313152400835</v>
       </c>
       <c r="E117" t="n">
-        <v>0.003360341786200109</v>
+        <v>0.002640426711624966</v>
       </c>
       <c r="F117" t="n">
-        <v>2.613541827821326</v>
+        <v>2.694892332499203</v>
+      </c>
+      <c r="G117" t="n">
+        <v>17.80566429287686</v>
       </c>
     </row>
     <row r="118">
@@ -8040,13 +9046,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D118" t="n">
-        <v>0.004148296593186373</v>
+        <v>0.004791231732776618</v>
       </c>
       <c r="E118" t="n">
-        <v>0.007110758362376031</v>
+        <v>0.006624130721355356</v>
       </c>
       <c r="F118" t="n">
-        <v>2.346276744994881</v>
+        <v>2.372579765044667</v>
+      </c>
+      <c r="G118" t="n">
+        <v>18.68641464756566</v>
       </c>
     </row>
     <row r="119">
@@ -8060,13 +9069,16 @@
         <v>6000000000</v>
       </c>
       <c r="D119" t="n">
-        <v>0.006593186372745491</v>
+        <v>0.006774530271398747</v>
       </c>
       <c r="E119" t="n">
-        <v>0.01040106001881602</v>
+        <v>0.01150939440424624</v>
       </c>
       <c r="F119" t="n">
-        <v>2.20099807594784</v>
+        <v>2.16104687824804</v>
+      </c>
+      <c r="G119" t="n">
+        <v>19.24202126042263</v>
       </c>
     </row>
     <row r="120">
@@ -8080,13 +9092,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D120" t="n">
-        <v>0.008376753507014029</v>
+        <v>0.008194154488517746</v>
       </c>
       <c r="E120" t="n">
-        <v>0.01369074874216469</v>
+        <v>0.01162087278610409</v>
       </c>
       <c r="F120" t="n">
-        <v>2.09121647296273</v>
+        <v>2.157214000467889</v>
+      </c>
+      <c r="G120" t="n">
+        <v>19.70180999093194</v>
       </c>
     </row>
     <row r="121">
@@ -8100,13 +9115,16 @@
         <v>7000000000</v>
       </c>
       <c r="D121" t="n">
-        <v>0.01084168336673347</v>
+        <v>0.009968684759916493</v>
       </c>
       <c r="E121" t="n">
-        <v>0.01552013025959124</v>
+        <v>0.0165215222327916</v>
       </c>
       <c r="F121" t="n">
-        <v>2.039631782611181</v>
+        <v>2.013544364816287</v>
+      </c>
+      <c r="G121" t="n">
+        <v>19.74083698899477</v>
       </c>
     </row>
     <row r="122">
@@ -8120,13 +9138,16 @@
         <v>7500000000</v>
       </c>
       <c r="D122" t="n">
-        <v>0.01230460921843687</v>
+        <v>0.01296450939457203</v>
       </c>
       <c r="E122" t="n">
-        <v>0.01843218757051486</v>
+        <v>0.02056895854310493</v>
       </c>
       <c r="F122" t="n">
-        <v>1.96726645500976</v>
+        <v>1.920058138872871</v>
+      </c>
+      <c r="G122" t="n">
+        <v>20.16516214217838</v>
       </c>
     </row>
     <row r="123">
@@ -8140,13 +9161,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D123" t="n">
-        <v>0.01234468937875752</v>
+        <v>0.01144050104384134</v>
       </c>
       <c r="E123" t="n">
-        <v>0.01887717226253909</v>
+        <v>0.01893803613077652</v>
       </c>
       <c r="F123" t="n">
-        <v>1.957070960752537</v>
+        <v>1.955692152966285</v>
+      </c>
+      <c r="G123" t="n">
+        <v>20.1525778180151</v>
       </c>
     </row>
     <row r="124">
@@ -8160,13 +9184,16 @@
         <v>8500000000</v>
       </c>
       <c r="D124" t="n">
-        <v>0.01260521042084168</v>
+        <v>0.01291231732776618</v>
       </c>
       <c r="E124" t="n">
-        <v>0.01958979910338077</v>
+        <v>0.01765284190156702</v>
       </c>
       <c r="F124" t="n">
-        <v>1.941155125677868</v>
+        <v>1.985631599452608</v>
+      </c>
+      <c r="G124" t="n">
+        <v>20.2447716928565</v>
       </c>
     </row>
     <row r="125">
@@ -8180,13 +9207,16 @@
         <v>9000000000</v>
       </c>
       <c r="D125" t="n">
-        <v>0.01361723446893788</v>
+        <v>0.01467640918580376</v>
       </c>
       <c r="E125" t="n">
-        <v>0.02129118000885632</v>
+        <v>0.02107611407264153</v>
       </c>
       <c r="F125" t="n">
-        <v>1.905027626713593</v>
+        <v>1.909458496381842</v>
+      </c>
+      <c r="G125" t="n">
+        <v>20.4601831323844</v>
       </c>
     </row>
     <row r="126">
@@ -8200,13 +9230,16 @@
         <v>9500000000</v>
       </c>
       <c r="D126" t="n">
-        <v>0.01633266533066132</v>
+        <v>0.01508350730688935</v>
       </c>
       <c r="E126" t="n">
-        <v>0.02426896373327721</v>
+        <v>0.02835153277553316</v>
       </c>
       <c r="F126" t="n">
-        <v>1.847206369354754</v>
+        <v>1.776782164955261</v>
+      </c>
+      <c r="G126" t="n">
+        <v>20.59938292266502</v>
       </c>
     </row>
     <row r="127">
@@ -8220,13 +9253,16 @@
         <v>10000000000</v>
       </c>
       <c r="D127" t="n">
-        <v>0.01773547094188377</v>
+        <v>0.01951983298538622</v>
       </c>
       <c r="E127" t="n">
-        <v>0.02679349306867807</v>
+        <v>0.03087031823822022</v>
       </c>
       <c r="F127" t="n">
-        <v>1.802611085337921</v>
+        <v>1.737375864047297</v>
+      </c>
+      <c r="G127" t="n">
+        <v>20.71290407636799</v>
       </c>
     </row>
     <row r="128">
@@ -8240,13 +9276,16 @@
         <v>1500000000</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2526553106212425</v>
+        <v>0.2521503131524008</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2488793467316994</v>
+        <v>0.2689881320764875</v>
       </c>
       <c r="F128" t="n">
-        <v>0.4348404276891686</v>
+        <v>0.3620673715584375</v>
+      </c>
+      <c r="G128" t="n">
+        <v>46.22202558814458</v>
       </c>
     </row>
     <row r="129">
@@ -8260,13 +9299,16 @@
         <v>2000000000</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1659619238476954</v>
+        <v>0.1652296450939457</v>
       </c>
       <c r="E129" t="n">
-        <v>0.1844047849775423</v>
+        <v>0.2033556974408026</v>
       </c>
       <c r="F129" t="n">
-        <v>0.6875343008847161</v>
+        <v>0.6093660137806769</v>
+      </c>
+      <c r="G129" t="n">
+        <v>31.51479255336698</v>
       </c>
     </row>
     <row r="130">
@@ -8280,13 +9322,16 @@
         <v>2500000000</v>
       </c>
       <c r="D130" t="n">
-        <v>0.01501002004008016</v>
+        <v>0.01538622129436326</v>
       </c>
       <c r="E130" t="n">
-        <v>0.023175750031336</v>
+        <v>0.02723699115234356</v>
       </c>
       <c r="F130" t="n">
-        <v>1.867713613406023</v>
+        <v>1.795136363246034</v>
+      </c>
+      <c r="G130" t="n">
+        <v>20.40880297349411</v>
       </c>
     </row>
     <row r="131">
@@ -8300,13 +9345,16 @@
         <v>3000000000</v>
       </c>
       <c r="D131" t="n">
-        <v>0.005170340681362726</v>
+        <v>0.004582463465553236</v>
       </c>
       <c r="E131" t="n">
-        <v>0.007982875437095197</v>
+        <v>0.009384370093929425</v>
       </c>
       <c r="F131" t="n">
-        <v>2.302843183829083</v>
+        <v>2.241016798262477</v>
+      </c>
+      <c r="G131" t="n">
+        <v>18.24573353035531</v>
       </c>
     </row>
     <row r="132">
@@ -8320,13 +9368,16 @@
         <v>3500000000</v>
       </c>
       <c r="D132" t="n">
-        <v>0.001613226452905812</v>
+        <v>0.001597077244258873</v>
       </c>
       <c r="E132" t="n">
-        <v>0.002522877457892064</v>
+        <v>0.002341186918247881</v>
       </c>
       <c r="F132" t="n">
-        <v>2.710031925039929</v>
+        <v>2.734729004656383</v>
+      </c>
+      <c r="G132" t="n">
+        <v>16.91473886773951</v>
       </c>
     </row>
     <row r="133">
@@ -8340,13 +9391,16 @@
         <v>4000000000</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0003507014028056112</v>
+        <v>0.0003653444676409186</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0007875926152541391</v>
+        <v>0.0007060432682570757</v>
       </c>
       <c r="F133" t="n">
-        <v>3.075677754830592</v>
+        <v>3.108125331631292</v>
+      </c>
+      <c r="G133" t="n">
+        <v>16.09805613751006</v>
       </c>
     </row>
     <row r="134">
@@ -8360,13 +9414,16 @@
         <v>4500000000</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0001803607214428858</v>
+        <v>0.0002400835073068894</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0003542446989906623</v>
+        <v>0.0003674845933087762</v>
       </c>
       <c r="F134" t="n">
-        <v>3.306512151716587</v>
+        <v>3.29621814240288</v>
+      </c>
+      <c r="G134" t="n">
+        <v>15.93862780726046</v>
       </c>
     </row>
     <row r="135">
@@ -8380,13 +9437,16 @@
         <v>5000000000</v>
       </c>
       <c r="D135" t="n">
-        <v>0.0002104208416833667</v>
+        <v>0.0003444676409185804</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0005728791275776845</v>
+        <v>0.0004513541505080073</v>
       </c>
       <c r="F135" t="n">
-        <v>3.16937383200192</v>
+        <v>3.238022997533533</v>
+      </c>
+      <c r="G135" t="n">
+        <v>16.52063844526461</v>
       </c>
     </row>
     <row r="136">
@@ -8400,13 +9460,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D136" t="n">
-        <v>0.001112224448897796</v>
+        <v>0.001210855949895616</v>
       </c>
       <c r="E136" t="n">
-        <v>0.001974429387132116</v>
+        <v>0.001967971449311128</v>
       </c>
       <c r="F136" t="n">
-        <v>2.790347788839678</v>
+        <v>2.791408219458365</v>
+      </c>
+      <c r="G136" t="n">
+        <v>17.3270122712747</v>
       </c>
     </row>
     <row r="137">
@@ -8420,13 +9483,16 @@
         <v>6000000000</v>
       </c>
       <c r="D137" t="n">
-        <v>0.001593186372745491</v>
+        <v>0.001805845511482255</v>
       </c>
       <c r="E137" t="n">
-        <v>0.002841734694011664</v>
+        <v>0.002739472932456351</v>
       </c>
       <c r="F137" t="n">
-        <v>2.670317330685177</v>
+        <v>2.682598609325635</v>
+      </c>
+      <c r="G137" t="n">
+        <v>17.82571782117943</v>
       </c>
     </row>
     <row r="138">
@@ -8440,13 +9506,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D138" t="n">
-        <v>0.002364729458917835</v>
+        <v>0.002338204592901879</v>
       </c>
       <c r="E138" t="n">
-        <v>0.003943535145990978</v>
+        <v>0.003942080053717295</v>
       </c>
       <c r="F138" t="n">
-        <v>2.558380563988619</v>
+        <v>2.558508881739787</v>
+      </c>
+      <c r="G138" t="n">
+        <v>18.19453589142532</v>
       </c>
     </row>
     <row r="139">
@@ -8460,13 +9529,16 @@
         <v>7000000000</v>
       </c>
       <c r="D139" t="n">
-        <v>0.00311623246492986</v>
+        <v>0.003058455114822547</v>
       </c>
       <c r="E139" t="n">
-        <v>0.004843637948663546</v>
+        <v>0.005975498511953907</v>
       </c>
       <c r="F139" t="n">
-        <v>2.486066908595232</v>
+        <v>2.410408615817615</v>
+      </c>
+      <c r="G139" t="n">
+        <v>17.9997543402632</v>
       </c>
     </row>
     <row r="140">
@@ -8480,13 +9552,16 @@
         <v>7500000000</v>
       </c>
       <c r="D140" t="n">
-        <v>0.003887775551102204</v>
+        <v>0.004196242171189979</v>
       </c>
       <c r="E140" t="n">
-        <v>0.006315782385557052</v>
+        <v>0.005987852903636562</v>
       </c>
       <c r="F140" t="n">
-        <v>2.390137057373543</v>
+        <v>2.409655093328649</v>
+      </c>
+      <c r="G140" t="n">
+        <v>19.29786104218447</v>
       </c>
     </row>
     <row r="141">
@@ -8500,13 +9575,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D141" t="n">
-        <v>0.003827655310621242</v>
+        <v>0.005187891440501044</v>
       </c>
       <c r="E141" t="n">
-        <v>0.005932938138226299</v>
+        <v>0.008770127979994838</v>
       </c>
       <c r="F141" t="n">
-        <v>2.413015001625501</v>
+        <v>2.267052677298753</v>
+      </c>
+      <c r="G141" t="n">
+        <v>19.67319005748564</v>
       </c>
     </row>
     <row r="142">
@@ -8520,13 +9598,16 @@
         <v>8500000000</v>
       </c>
       <c r="D142" t="n">
-        <v>0.003647294589178357</v>
+        <v>0.004467640918580376</v>
       </c>
       <c r="E142" t="n">
-        <v>0.005708918520593204</v>
+        <v>0.007596827875920454</v>
       </c>
       <c r="F142" t="n">
-        <v>2.427011275032837</v>
+        <v>2.321530913421873</v>
+      </c>
+      <c r="G142" t="n">
+        <v>18.27114932056562</v>
       </c>
     </row>
     <row r="143">
@@ -8540,13 +9621,16 @@
         <v>9000000000</v>
       </c>
       <c r="D143" t="n">
-        <v>0.004649298597194389</v>
+        <v>0.004530271398747391</v>
       </c>
       <c r="E143" t="n">
-        <v>0.00676539318209891</v>
+        <v>0.005753150419219196</v>
       </c>
       <c r="F143" t="n">
-        <v>2.364774574442033</v>
+        <v>2.424209919743255</v>
+      </c>
+      <c r="G143" t="n">
+        <v>18.4951852119942</v>
       </c>
     </row>
     <row r="144">
@@ -8560,13 +9644,16 @@
         <v>9500000000</v>
       </c>
       <c r="D144" t="n">
-        <v>0.005430861723446894</v>
+        <v>0.004926931106471816</v>
       </c>
       <c r="E144" t="n">
-        <v>0.008176739636092931</v>
+        <v>0.007996562871141605</v>
       </c>
       <c r="F144" t="n">
-        <v>2.293753895767566</v>
+        <v>2.302195180384911</v>
+      </c>
+      <c r="G144" t="n">
+        <v>18.57631410759065</v>
       </c>
     </row>
     <row r="145">
@@ -8580,13 +9667,16 @@
         <v>10000000000</v>
       </c>
       <c r="D145" t="n">
-        <v>0.005971943887775551</v>
+        <v>0.006064718162839248</v>
       </c>
       <c r="E145" t="n">
-        <v>0.009360459687551019</v>
+        <v>0.007275582947268788</v>
       </c>
       <c r="F145" t="n">
-        <v>2.242002266318396</v>
+        <v>2.337724304556686</v>
+      </c>
+      <c r="G145" t="n">
+        <v>18.8537239720291</v>
       </c>
     </row>
     <row r="146">
@@ -8600,13 +9690,16 @@
         <v>1500000000</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2514428857715431</v>
+        <v>0.2513883089770355</v>
       </c>
       <c r="E146" t="n">
-        <v>0.2469745225770082</v>
+        <v>0.250961120410513</v>
       </c>
       <c r="F146" t="n">
-        <v>0.4418486559505302</v>
+        <v>0.4272055017239784</v>
+      </c>
+      <c r="G146" t="n">
+        <v>46.93344862930008</v>
       </c>
     </row>
     <row r="147">
@@ -8620,13 +9713,16 @@
         <v>2000000000</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1618837675350701</v>
+        <v>0.1608455114822547</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1809469281660931</v>
+        <v>0.189339456908196</v>
       </c>
       <c r="F147" t="n">
-        <v>0.7022469963040138</v>
+        <v>0.6667916635333581</v>
+      </c>
+      <c r="G147" t="n">
+        <v>32.00341615454362</v>
       </c>
     </row>
     <row r="148">
@@ -8640,13 +9736,16 @@
         <v>2500000000</v>
       </c>
       <c r="D148" t="n">
-        <v>0.01159318637274549</v>
+        <v>0.01127348643006263</v>
       </c>
       <c r="E148" t="n">
-        <v>0.01834579555164638</v>
+        <v>0.02061890876074926</v>
       </c>
       <c r="F148" t="n">
-        <v>1.969269763017137</v>
+        <v>1.919004560477157</v>
+      </c>
+      <c r="G148" t="n">
+        <v>19.92816172085804</v>
       </c>
     </row>
     <row r="149">
@@ -8660,13 +9759,16 @@
         <v>3000000000</v>
       </c>
       <c r="D149" t="n">
-        <v>0.003106212424849699</v>
+        <v>0.003277661795407098</v>
       </c>
       <c r="E149" t="n">
-        <v>0.005398793180027848</v>
+        <v>0.005678339352512126</v>
       </c>
       <c r="F149" t="n">
-        <v>2.447207775361786</v>
+        <v>2.428959151223089</v>
+      </c>
+      <c r="G149" t="n">
+        <v>17.68686770649173</v>
       </c>
     </row>
     <row r="150">
@@ -8680,13 +9782,16 @@
         <v>3500000000</v>
       </c>
       <c r="D150" t="n">
-        <v>0.0006412825651302605</v>
+        <v>0.0007098121085594989</v>
       </c>
       <c r="E150" t="n">
-        <v>0.001219655148357748</v>
+        <v>0.001441480164565213</v>
       </c>
       <c r="F150" t="n">
-        <v>2.942816276775615</v>
+        <v>2.890691946366774</v>
+      </c>
+      <c r="G150" t="n">
+        <v>16.37521943426193</v>
       </c>
     </row>
     <row r="151">
@@ -8700,13 +9805,16 @@
         <v>4000000000</v>
       </c>
       <c r="D151" t="n">
-        <v>7.014028056112224e-05</v>
+        <v>2.087682672233821e-05</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0001886457549028411</v>
+        <v>0.0001005557956687888</v>
       </c>
       <c r="F151" t="n">
-        <v>3.47912421853886</v>
+        <v>3.644272896311691</v>
+      </c>
+      <c r="G151" t="n">
+        <v>15.4019190502865</v>
       </c>
     </row>
     <row r="152">
@@ -8720,13 +9828,16 @@
         <v>4500000000</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1.04384133611691e-05</v>
       </c>
       <c r="E152" t="n">
-        <v>3.355151650413341e-05</v>
+        <v>5.315562179270347e-05</v>
       </c>
       <c r="F152" t="n">
-        <v>3.917503598450601</v>
+        <v>3.805097532825424</v>
+      </c>
+      <c r="G152" t="n">
+        <v>15.02775464091628</v>
       </c>
     </row>
     <row r="153">
@@ -8740,13 +9851,16 @@
         <v>5000000000</v>
       </c>
       <c r="D153" t="n">
-        <v>1.002004008016032e-05</v>
+        <v>1.04384133611691e-05</v>
       </c>
       <c r="E153" t="n">
-        <v>6.078765259690457e-05</v>
+        <v>3.744040377071632e-05</v>
       </c>
       <c r="F153" t="n">
-        <v>3.771759577751392</v>
+        <v>3.890977779692311</v>
+      </c>
+      <c r="G153" t="n">
+        <v>15.57533180625552</v>
       </c>
     </row>
     <row r="154">
@@ -8760,13 +9874,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D154" t="n">
-        <v>0.0001803607214428858</v>
+        <v>0.0002192066805845511</v>
       </c>
       <c r="E154" t="n">
-        <v>0.0003542945482950451</v>
+        <v>0.0003796678253595613</v>
       </c>
       <c r="F154" t="n">
-        <v>3.306472730033427</v>
+        <v>3.287044722415093</v>
+      </c>
+      <c r="G154" t="n">
+        <v>16.18027177191031</v>
       </c>
     </row>
     <row r="155">
@@ -8780,13 +9897,16 @@
         <v>6000000000</v>
       </c>
       <c r="D155" t="n">
-        <v>0.0003507014028056112</v>
+        <v>0.0001670146137787056</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0006291805118745985</v>
+        <v>0.0007538112458151025</v>
       </c>
       <c r="F155" t="n">
-        <v>3.142028907557206</v>
+        <v>3.088726599573925</v>
+      </c>
+      <c r="G155" t="n">
+        <v>16.66149448119027</v>
       </c>
     </row>
     <row r="156">
@@ -8800,13 +9920,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0005811623246492986</v>
+        <v>0.0003757828810020877</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0007829753057932572</v>
+        <v>0.0007923616169999118</v>
       </c>
       <c r="F156" t="n">
-        <v>3.077430650856512</v>
+        <v>3.073877137869671</v>
+      </c>
+      <c r="G156" t="n">
+        <v>16.96676140575508</v>
       </c>
     </row>
     <row r="157">
@@ -8820,13 +9943,16 @@
         <v>7000000000</v>
       </c>
       <c r="D157" t="n">
-        <v>0.0004509018036072144</v>
+        <v>0.0007620041753653445</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0009202900107347358</v>
+        <v>0.001008617267062924</v>
       </c>
       <c r="F157" t="n">
-        <v>3.028943383255017</v>
+        <v>3.001147094123848</v>
+      </c>
+      <c r="G157" t="n">
+        <v>17.42558078767177</v>
       </c>
     </row>
     <row r="158">
@@ -8840,13 +9966,16 @@
         <v>7500000000</v>
       </c>
       <c r="D158" t="n">
-        <v>0.0008016032064128256</v>
+        <v>0.001137787056367432</v>
       </c>
       <c r="E158" t="n">
-        <v>0.00112339886098626</v>
+        <v>0.001326518776953384</v>
       </c>
       <c r="F158" t="n">
-        <v>2.968175706713211</v>
+        <v>2.916715434426666</v>
+      </c>
+      <c r="G158" t="n">
+        <v>16.92606221574745</v>
       </c>
     </row>
     <row r="159">
@@ -8860,13 +9989,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D159" t="n">
-        <v>0.0006513026052104208</v>
+        <v>0.0007306889352818372</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0013154358337693</v>
+        <v>0.001380203143664907</v>
       </c>
       <c r="F159" t="n">
-        <v>2.91933157730813</v>
+        <v>2.904317956781152</v>
+      </c>
+      <c r="G159" t="n">
+        <v>16.63887023526</v>
       </c>
     </row>
     <row r="160">
@@ -8880,13 +10012,16 @@
         <v>8500000000</v>
       </c>
       <c r="D160" t="n">
-        <v>0.000751503006012024</v>
+        <v>0.0007098121085594989</v>
       </c>
       <c r="E160" t="n">
-        <v>0.001171338597296522</v>
+        <v>0.001295038508131069</v>
       </c>
       <c r="F160" t="n">
-        <v>2.955308088089091</v>
+        <v>2.92419926133506</v>
+      </c>
+      <c r="G160" t="n">
+        <v>16.63501298476573</v>
       </c>
     </row>
     <row r="161">
@@ -8900,13 +10035,16 @@
         <v>9000000000</v>
       </c>
       <c r="D161" t="n">
-        <v>0.0007715430861723447</v>
+        <v>0.0009812108559498955</v>
       </c>
       <c r="E161" t="n">
-        <v>0.001317917137371659</v>
+        <v>0.001131033541434741</v>
       </c>
       <c r="F161" t="n">
-        <v>2.918744124713062</v>
+        <v>2.966093332628138</v>
+      </c>
+      <c r="G161" t="n">
+        <v>16.79246747429634</v>
       </c>
     </row>
     <row r="162">
@@ -8920,13 +10058,16 @@
         <v>9500000000</v>
       </c>
       <c r="D162" t="n">
-        <v>0.001062124248496994</v>
+        <v>0.0009498956158663883</v>
       </c>
       <c r="E162" t="n">
-        <v>0.001552879362256474</v>
+        <v>0.002232176438292995</v>
       </c>
       <c r="F162" t="n">
-        <v>2.86721532465254</v>
+        <v>2.750388172120075</v>
+      </c>
+      <c r="G162" t="n">
+        <v>16.87148419832865</v>
       </c>
     </row>
     <row r="163">
@@ -8940,13 +10081,16 @@
         <v>10000000000</v>
       </c>
       <c r="D163" t="n">
-        <v>0.001152304609218437</v>
+        <v>0.00115866388308977</v>
       </c>
       <c r="E163" t="n">
-        <v>0.00194223927386018</v>
+        <v>0.001725759879474859</v>
       </c>
       <c r="F163" t="n">
-        <v>2.795665054056381</v>
+        <v>2.833646118006445</v>
+      </c>
+      <c r="G163" t="n">
+        <v>17.12939657934978</v>
       </c>
     </row>
     <row r="164">
@@ -8960,13 +10104,16 @@
         <v>1500000000</v>
       </c>
       <c r="D164" t="n">
-        <v>0.2516132264529058</v>
+        <v>0.2534342379958247</v>
       </c>
       <c r="E164" t="n">
-        <v>0.2489887209343036</v>
+        <v>0.2448485131835703</v>
       </c>
       <c r="F164" t="n">
-        <v>0.4344386690799037</v>
+        <v>0.4496963986259778</v>
+      </c>
+      <c r="G164" t="n">
+        <v>43.92852023811554</v>
       </c>
     </row>
     <row r="165">
@@ -8980,13 +10127,16 @@
         <v>2000000000</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1640781563126253</v>
+        <v>0.1645720250521921</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1855251525164666</v>
+        <v>0.1793284109936665</v>
       </c>
       <c r="F165" t="n">
-        <v>0.6827991924460026</v>
+        <v>0.7091859422682169</v>
+      </c>
+      <c r="G165" t="n">
+        <v>30.2305065370897</v>
       </c>
     </row>
     <row r="166">
@@ -9000,13 +10150,16 @@
         <v>2500000000</v>
       </c>
       <c r="D166" t="n">
-        <v>0.01020040080160321</v>
+        <v>0.01174321503131524</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0178492734197806</v>
+        <v>0.01785705373101941</v>
       </c>
       <c r="F166" t="n">
-        <v>1.980939466571299</v>
+        <v>1.980754514938926</v>
+      </c>
+      <c r="G166" t="n">
+        <v>19.84677826189671</v>
       </c>
     </row>
     <row r="167">
@@ -9020,13 +10173,16 @@
         <v>3000000000</v>
       </c>
       <c r="D167" t="n">
-        <v>0.002034068136272545</v>
+        <v>0.002233820459290188</v>
       </c>
       <c r="E167" t="n">
-        <v>0.004202324830330397</v>
+        <v>0.00438705569726466</v>
       </c>
       <c r="F167" t="n">
-        <v>2.536202242749532</v>
+        <v>2.521101347667772</v>
+      </c>
+      <c r="G167" t="n">
+        <v>17.3528540132304</v>
       </c>
     </row>
     <row r="168">
@@ -9040,13 +10196,16 @@
         <v>3500000000</v>
       </c>
       <c r="D168" t="n">
-        <v>0.0002705410821643287</v>
+        <v>0.0002087682672233821</v>
       </c>
       <c r="E168" t="n">
-        <v>0.000636795799867689</v>
+        <v>0.0006679324189244468</v>
       </c>
       <c r="F168" t="n">
-        <v>3.138504697403989</v>
+        <v>3.124487132888664</v>
+      </c>
+      <c r="G168" t="n">
+        <v>15.71778079791283</v>
       </c>
     </row>
     <row r="169">
@@ -9060,13 +10219,16 @@
         <v>4000000000</v>
       </c>
       <c r="D169" t="n">
-        <v>2.004008016032064e-05</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>4.40708441633691e-05</v>
+        <v>6.45968154572638e-05</v>
       </c>
       <c r="F169" t="n">
-        <v>3.851237927134874</v>
+        <v>3.75656989759786</v>
+      </c>
+      <c r="G169" t="n">
+        <v>14.82681171375954</v>
       </c>
     </row>
     <row r="170">
@@ -9083,10 +10245,13 @@
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>2.89968744624257e-06</v>
+        <v>1.231170496105773e-06</v>
       </c>
       <c r="F170" t="n">
-        <v>4.472459637867975</v>
+        <v>4.652262900130434</v>
+      </c>
+      <c r="G170" t="n">
+        <v>14.37808730029337</v>
       </c>
     </row>
     <row r="171">
@@ -9103,10 +10268,13 @@
         <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>3.507745970414148e-06</v>
+        <v>1.19324117345054e-05</v>
       </c>
       <c r="F171" t="n">
-        <v>4.43159198656227</v>
+        <v>4.160035848817281</v>
+      </c>
+      <c r="G171" t="n">
+        <v>14.82727540886309</v>
       </c>
     </row>
     <row r="172">
@@ -9120,13 +10288,16 @@
         <v>5499999999.999999</v>
       </c>
       <c r="D172" t="n">
-        <v>2.004008016032064e-05</v>
+        <v>2.087682672233821e-05</v>
       </c>
       <c r="E172" t="n">
-        <v>4.971772260664818e-05</v>
+        <v>7.105526269814033e-05</v>
       </c>
       <c r="F172" t="n">
-        <v>3.821614941137458</v>
+        <v>3.73264347766462</v>
+      </c>
+      <c r="G172" t="n">
+        <v>15.45540090554531</v>
       </c>
     </row>
     <row r="173">
@@ -9140,13 +10311,16 @@
         <v>6000000000</v>
       </c>
       <c r="D173" t="n">
-        <v>7.014028056112224e-05</v>
+        <v>3.131524008350731e-05</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0001200327784235475</v>
+        <v>9.027555695789357e-05</v>
       </c>
       <c r="F173" t="n">
-        <v>3.598475978214851</v>
+        <v>3.671920243120411</v>
+      </c>
+      <c r="G173" t="n">
+        <v>15.90925550228934</v>
       </c>
     </row>
     <row r="174">
@@ -9160,13 +10334,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D174" t="n">
-        <v>7.014028056112224e-05</v>
+        <v>6.263048016701462e-05</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0001220389119608605</v>
+        <v>0.0001020510508267175</v>
       </c>
       <c r="F174" t="n">
-        <v>3.594162171365793</v>
+        <v>3.640474428542003</v>
+      </c>
+      <c r="G174" t="n">
+        <v>16.12949292130886</v>
       </c>
     </row>
     <row r="175">
@@ -9180,13 +10357,16 @@
         <v>7000000000</v>
       </c>
       <c r="D175" t="n">
-        <v>7.014028056112224e-05</v>
+        <v>9.394572025052193e-05</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0001363966378419604</v>
+        <v>0.0002125686226447046</v>
       </c>
       <c r="F175" t="n">
-        <v>3.565095036640729</v>
+        <v>3.446999486096627</v>
+      </c>
+      <c r="G175" t="n">
+        <v>15.49861232454484</v>
       </c>
     </row>
     <row r="176">
@@ -9200,13 +10380,16 @@
         <v>7500000000</v>
       </c>
       <c r="D176" t="n">
-        <v>1.002004008016032e-05</v>
+        <v>4.175365344467641e-05</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0001026371358348804</v>
+        <v>0.0001530602432578031</v>
       </c>
       <c r="F176" t="n">
-        <v>3.638999784130525</v>
+        <v>3.53475030926486</v>
+      </c>
+      <c r="G176" t="n">
+        <v>17.11472813807696</v>
       </c>
     </row>
     <row r="177">
@@ -9220,13 +10403,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D177" t="n">
-        <v>9.018036072144289e-05</v>
+        <v>0.0001565762004175365</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0001657296907167107</v>
+        <v>0.0001457759704008689</v>
       </c>
       <c r="F177" t="n">
-        <v>3.51367941524251</v>
+        <v>3.547615056101199</v>
+      </c>
+      <c r="G177" t="n">
+        <v>17.35402471572995</v>
       </c>
     </row>
     <row r="178">
@@ -9240,13 +10426,16 @@
         <v>8500000000</v>
       </c>
       <c r="D178" t="n">
-        <v>5.01002004008016e-05</v>
+        <v>6.263048016701462e-05</v>
       </c>
       <c r="E178" t="n">
-        <v>0.000122710156649763</v>
+        <v>0.0001019060610950949</v>
       </c>
       <c r="F178" t="n">
-        <v>3.592733597546584</v>
+        <v>3.640840460811127</v>
+      </c>
+      <c r="G178" t="n">
+        <v>15.32987860330659</v>
       </c>
     </row>
     <row r="179">
@@ -9260,13 +10449,16 @@
         <v>9000000000</v>
       </c>
       <c r="D179" t="n">
-        <v>5.01002004008016e-05</v>
+        <v>6.263048016701462e-05</v>
       </c>
       <c r="E179" t="n">
-        <v>0.000122062535716027</v>
+        <v>8.921615504921646e-05</v>
       </c>
       <c r="F179" t="n">
-        <v>3.594111769490271</v>
+        <v>3.674935246055168</v>
+      </c>
+      <c r="G179" t="n">
+        <v>15.46258966577484</v>
       </c>
     </row>
     <row r="180">
@@ -9280,13 +10472,16 @@
         <v>9500000000</v>
       </c>
       <c r="D180" t="n">
-        <v>4.008016032064128e-05</v>
+        <v>0.0001670146137787056</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0001638659039118217</v>
+        <v>0.0001877198053973875</v>
       </c>
       <c r="F180" t="n">
-        <v>3.516682741418855</v>
+        <v>3.480442560907775</v>
+      </c>
+      <c r="G180" t="n">
+        <v>16.48083177896169</v>
       </c>
     </row>
     <row r="181">
@@ -9300,13 +10495,16 @@
         <v>10000000000</v>
       </c>
       <c r="D181" t="n">
-        <v>7.014028056112224e-05</v>
+        <v>0.0001774530271398747</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0001987038604036492</v>
+        <v>0.0002364127816703261</v>
       </c>
       <c r="F181" t="n">
-        <v>3.465179867428585</v>
+        <v>3.418171329550147</v>
+      </c>
+      <c r="G181" t="n">
+        <v>15.76450208191863</v>
       </c>
     </row>
     <row r="182">
@@ -9320,13 +10518,16 @@
         <v>1500000000</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2506012024048096</v>
+        <v>0.2541753653444677</v>
       </c>
       <c r="E182" t="n">
-        <v>0.2469533370597078</v>
+        <v>0.2427741256957848</v>
       </c>
       <c r="F182" t="n">
-        <v>0.4419267232113248</v>
+        <v>0.4573803738238779</v>
+      </c>
+      <c r="G182" t="n">
+        <v>47.23267602756226</v>
       </c>
     </row>
     <row r="183">
@@ -9340,13 +10541,16 @@
         <v>2000000000</v>
       </c>
       <c r="D183" t="n">
-        <v>0.1626953907815631</v>
+        <v>0.1632150313152401</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1810003068898424</v>
+        <v>0.1863023193793438</v>
       </c>
       <c r="F183" t="n">
-        <v>0.7020187265367682</v>
+        <v>0.6795235596961431</v>
+      </c>
+      <c r="G183" t="n">
+        <v>31.37350103989531</v>
       </c>
     </row>
     <row r="184">
@@ -9360,13 +10564,16 @@
         <v>2500000000</v>
       </c>
       <c r="D184" t="n">
-        <v>0.008486973947895791</v>
+        <v>0.008465553235908143</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0157959050418643</v>
+        <v>0.01464075831092582</v>
       </c>
       <c r="F184" t="n">
-        <v>2.032308708170935</v>
+        <v>2.063743715337148</v>
+      </c>
+      <c r="G184" t="n">
+        <v>19.60645710167308</v>
       </c>
     </row>
     <row r="185">
@@ -9380,13 +10587,16 @@
         <v>3000000000</v>
       </c>
       <c r="D185" t="n">
-        <v>0.001773547094188377</v>
+        <v>0.001889352818371607</v>
       </c>
       <c r="E185" t="n">
-        <v>0.003520508071430286</v>
+        <v>0.003426777490208993</v>
       </c>
       <c r="F185" t="n">
-        <v>2.597591094430469</v>
+        <v>2.606844933870235</v>
+      </c>
+      <c r="G185" t="n">
+        <v>17.07886036578558</v>
       </c>
     </row>
     <row r="186">
@@ -9400,13 +10610,16 @@
         <v>3500000000</v>
       </c>
       <c r="D186" t="n">
-        <v>0.0001202404809619239</v>
+        <v>0.0001148225469728601</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0003836177570704138</v>
+        <v>0.000369867176327704</v>
       </c>
       <c r="F186" t="n">
-        <v>3.284129049206173</v>
+        <v>3.294402237708638</v>
+      </c>
+      <c r="G186" t="n">
+        <v>15.51729317858266</v>
       </c>
     </row>
     <row r="187">
@@ -9423,10 +10636,13 @@
         <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>1.297341044627028e-05</v>
+        <v>9.15461143707346e-06</v>
       </c>
       <c r="F187" t="n">
-        <v>4.140892146213246</v>
+        <v>4.220165558057103</v>
+      </c>
+      <c r="G187" t="n">
+        <v>14.48111987384656</v>
       </c>
     </row>
     <row r="188">
@@ -9443,10 +10659,13 @@
         <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>1.905435802255453e-07</v>
+        <v>2.53142720637703e-07</v>
       </c>
       <c r="F188" t="n">
-        <v>5.023222499556581</v>
+        <v>4.968408253541797</v>
+      </c>
+      <c r="G188" t="n">
+        <v>14.01681229694995</v>
       </c>
     </row>
     <row r="189">
@@ -9463,10 +10682,13 @@
         <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>2.016866890824087e-07</v>
+        <v>3.051839681333068e-07</v>
       </c>
       <c r="F189" t="n">
-        <v>5.012300528535191</v>
+        <v>4.932022855447681</v>
+      </c>
+      <c r="G189" t="n">
+        <v>14.43818320420581</v>
       </c>
     </row>
     <row r="190">
@@ -9483,10 +10705,13 @@
         <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>7.471830385366149e-06</v>
+        <v>1.514183180068879e-05</v>
       </c>
       <c r="F190" t="n">
-        <v>4.265730915879066</v>
+        <v>4.105304766371179</v>
+      </c>
+      <c r="G190" t="n">
+        <v>14.99782842982044</v>
       </c>
     </row>
     <row r="191">
@@ -9503,10 +10728,13 @@
         <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>1.218210586473955e-05</v>
+        <v>1.4254774050883e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>4.155303413572788</v>
+        <v>4.119238035954746</v>
+      </c>
+      <c r="G191" t="n">
+        <v>15.33709508600049</v>
       </c>
     </row>
     <row r="192">
@@ -9520,13 +10748,16 @@
         <v>6499999999.999999</v>
       </c>
       <c r="D192" t="n">
-        <v>2.004008016032064e-05</v>
+        <v>1.04384133611691e-05</v>
       </c>
       <c r="E192" t="n">
-        <v>1.369052330443394e-05</v>
+        <v>1.154206778057934e-05</v>
       </c>
       <c r="F192" t="n">
-        <v>4.128535789022623</v>
+        <v>4.167625935134375</v>
+      </c>
+      <c r="G192" t="n">
+        <v>15.54722558073415</v>
       </c>
     </row>
     <row r="193">
@@ -9540,13 +10771,16 @@
         <v>7000000000</v>
       </c>
       <c r="D193" t="n">
-        <v>1.002004008016032e-05</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>1.494949360089334e-05</v>
+        <v>2.098761700240024e-05</v>
       </c>
       <c r="F193" t="n">
-        <v>4.108258848438194</v>
+        <v>4.029200041583389</v>
+      </c>
+      <c r="G193" t="n">
+        <v>14.8013838642544</v>
       </c>
     </row>
     <row r="194">
@@ -9563,10 +10797,13 @@
         <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>4.838444229420929e-06</v>
+        <v>4.157433214742599e-06</v>
       </c>
       <c r="F194" t="n">
-        <v>4.361751819658988</v>
+        <v>4.394819399273038</v>
+      </c>
+      <c r="G194" t="n">
+        <v>16.45965420819375</v>
       </c>
     </row>
     <row r="195">
@@ -9580,13 +10817,16 @@
         <v>7999999999.999999</v>
       </c>
       <c r="D195" t="n">
-        <v>2.004008016032064e-05</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>6.758352020756481e-06</v>
+        <v>2.993177451492727e-06</v>
       </c>
       <c r="F195" t="n">
-        <v>4.288081808971464</v>
+        <v>4.465671332651231</v>
+      </c>
+      <c r="G195" t="n">
+        <v>16.65332440643963</v>
       </c>
     </row>
     <row r="196">
@@ -9603,10 +10843,13 @@
         <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>6.51890437034158e-06</v>
+        <v>8.210090805269861e-06</v>
       </c>
       <c r="F196" t="n">
-        <v>4.296089463248127</v>
+        <v>4.244649098772985</v>
+      </c>
+      <c r="G196" t="n">
+        <v>14.5407109121043</v>
       </c>
     </row>
     <row r="197">
@@ -9620,13 +10863,16 @@
         <v>9000000000</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>1.04384133611691e-05</v>
       </c>
       <c r="E197" t="n">
-        <v>5.231743113370172e-06</v>
+        <v>6.307638588494208e-06</v>
       </c>
       <c r="F197" t="n">
-        <v>4.344625997754192</v>
+        <v>4.303390898840878</v>
+      </c>
+      <c r="G197" t="n">
+        <v>15.55396589288585</v>
       </c>
     </row>
     <row r="198">
@@ -9643,10 +10889,13 @@
         <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>6.693243955783386e-06</v>
+        <v>6.038214203701547e-06</v>
       </c>
       <c r="F198" t="n">
-        <v>4.290232068932872</v>
+        <v>4.313048132947223</v>
+      </c>
+      <c r="G198" t="n">
+        <v>14.61783266143221</v>
       </c>
     </row>
     <row r="199">
@@ -9660,13 +10909,16 @@
         <v>10000000000</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>1.04384133611691e-05</v>
       </c>
       <c r="E199" t="n">
-        <v>7.947579423228641e-06</v>
+        <v>9.498879654470052e-06</v>
       </c>
       <c r="F199" t="n">
-        <v>4.251930696850531</v>
+        <v>4.211835971403133</v>
+      </c>
+      <c r="G199" t="n">
+        <v>15.65547646447841</v>
       </c>
     </row>
     <row r="200">
@@ -9680,13 +10932,16 @@
         <v>1500000000</v>
       </c>
       <c r="D200" t="n">
-        <v>0.2496793587174349</v>
+        <v>0.2491544885177453</v>
       </c>
       <c r="E200" t="n">
-        <v>0.2484231610599365</v>
+        <v>0.2630982275315502</v>
       </c>
       <c r="F200" t="n">
-        <v>0.4365168689766369</v>
+        <v>0.3831679050600685</v>
+      </c>
+      <c r="G200" t="n">
+        <v>42.37791348173676</v>
       </c>
     </row>
     <row r="201">
@@ -9700,13 +10955,16 @@
         <v>2000000000</v>
       </c>
       <c r="D201" t="n">
-        <v>0.1596993987975952</v>
+        <v>0.1601356993736952</v>
       </c>
       <c r="E201" t="n">
-        <v>0.180797945558773</v>
+        <v>0.1917646893421985</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7028843019934234</v>
+        <v>0.6567020673138501</v>
+      </c>
+      <c r="G201" t="n">
+        <v>30.5516831400708</v>
       </c>
     </row>
     <row r="202">
@@ -9720,13 +10978,16 @@
         <v>2500000000</v>
       </c>
       <c r="D202" t="n">
-        <v>0.008547094188376753</v>
+        <v>0.009102296450939457</v>
       </c>
       <c r="E202" t="n">
-        <v>0.01482967320103606</v>
+        <v>0.0165715147719252</v>
       </c>
       <c r="F202" t="n">
-        <v>2.058462106513209</v>
+        <v>2.012277374846932</v>
+      </c>
+      <c r="G202" t="n">
+        <v>19.54298203095777</v>
       </c>
     </row>
     <row r="203">
@@ -9740,13 +11001,16 @@
         <v>3000000000</v>
       </c>
       <c r="D203" t="n">
-        <v>0.001633266533066132</v>
+        <v>0.001430062630480167</v>
       </c>
       <c r="E203" t="n">
-        <v>0.003019891984195004</v>
+        <v>0.003070187984034021</v>
       </c>
       <c r="F203" t="n">
-        <v>2.64983767231916</v>
+        <v>2.644251991997193</v>
+      </c>
+      <c r="G203" t="n">
+        <v>16.98178139829023</v>
       </c>
     </row>
     <row r="204">
@@ -9760,13 +11024,16 @@
         <v>3500000000</v>
       </c>
       <c r="D204" t="n">
-        <v>6.012024048096193e-05</v>
+        <v>5.219206680584551e-05</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0002735828011550225</v>
+        <v>0.0002877470740917384</v>
       </c>
       <c r="F204" t="n">
-        <v>3.378224802517847</v>
+        <v>3.364319875771857</v>
+      </c>
+      <c r="G204" t="n">
+        <v>15.3253882659017</v>
       </c>
     </row>
     <row r="205">
@@ -9783,10 +11050,13 @@
         <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>3.822089487434128e-06</v>
+        <v>4.463631173847321e-06</v>
       </c>
       <c r="F205" t="n">
-        <v>4.413054371745903</v>
+        <v>4.379356696268901</v>
+      </c>
+      <c r="G205" t="n">
+        <v>14.22774591948122</v>
       </c>
     </row>
     <row r="206">
@@ -9803,10 +11073,13 @@
         <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>1.070459500269887e-08</v>
+        <v>7.083849588277369e-09</v>
       </c>
       <c r="F206" t="n">
-        <v>5.55013084686262</v>
+        <v>5.621868849991369</v>
+      </c>
+      <c r="G206" t="n">
+        <v>13.80376149677422</v>
       </c>
     </row>
     <row r="207">
@@ -9823,10 +11096,13 @@
         <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>7.186431757752532e-09</v>
+        <v>3.5146564368182e-09</v>
       </c>
       <c r="F207" t="n">
-        <v>5.619385185534386</v>
+        <v>5.741711916669529</v>
+      </c>
+      <c r="G207" t="n">
+        <v>14.18858099662451</v>
       </c>
     </row>
     <row r="208">
@@ -9843,10 +11119,13 @@
         <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>9.53556586962129e-07</v>
+        <v>5.943656367374552e-07</v>
       </c>
       <c r="F208" t="n">
-        <v>4.704666112992036</v>
+        <v>4.800212320440256</v>
+      </c>
+      <c r="G208" t="n">
+        <v>14.66444415847099</v>
       </c>
     </row>
     <row r="209">
@@ -9863,10 +11142,13 @@
         <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>1.833862025069938e-06</v>
+        <v>2.092125598128655e-06</v>
       </c>
       <c r="F209" t="n">
-        <v>4.569439685511886</v>
+        <v>4.541746826725797</v>
+      </c>
+      <c r="G209" t="n">
+        <v>15.00075174531505</v>
       </c>
     </row>
     <row r="210">
@@ -9883,10 +11165,13 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>1.307152339608905e-06</v>
+        <v>1.726735869176282e-06</v>
       </c>
       <c r="F210" t="n">
-        <v>4.639902285951792</v>
+        <v>4.582039495550496</v>
+      </c>
+      <c r="G210" t="n">
+        <v>15.15213801399784</v>
       </c>
     </row>
     <row r="211">
@@ -9903,10 +11188,13 @@
         <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>1.026235540707946e-06</v>
+        <v>8.259975657563914e-07</v>
       </c>
       <c r="F211" t="n">
-        <v>4.689657434890895</v>
+        <v>4.733881812268996</v>
+      </c>
+      <c r="G211" t="n">
+        <v>14.35468472473488</v>
       </c>
     </row>
     <row r="212">
@@ -9923,10 +11211,13 @@
         <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>7.236943371028666e-08</v>
+        <v>5.009471469508839e-08</v>
       </c>
       <c r="F212" t="n">
-        <v>5.205970642679001</v>
+        <v>5.273857145466687</v>
+      </c>
+      <c r="G212" t="n">
+        <v>16.0427172369126</v>
       </c>
     </row>
     <row r="213">
@@ -9943,10 +11234,13 @@
         <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>8.00091878531427e-08</v>
+        <v>1.318925202190531e-07</v>
       </c>
       <c r="F213" t="n">
-        <v>5.187306142565967</v>
+        <v>5.093392027568907</v>
+      </c>
+      <c r="G213" t="n">
+        <v>16.20703655366158</v>
       </c>
     </row>
     <row r="214">
@@ -9963,10 +11257,13 @@
         <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>1.057173921228103e-07</v>
+        <v>8.08756695816628e-08</v>
       </c>
       <c r="F214" t="n">
-        <v>5.135154024710753</v>
+        <v>5.185299106776969</v>
+      </c>
+      <c r="G214" t="n">
+        <v>16.27288925397428</v>
       </c>
     </row>
     <row r="215">
@@ -9983,10 +11280,13 @@
         <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>6.652221006109441e-08</v>
+        <v>2.621596266421226e-08</v>
       </c>
       <c r="F215" t="n">
-        <v>5.221590854119876</v>
+        <v>5.391404180343043</v>
+      </c>
+      <c r="G215" t="n">
+        <v>15.02246293867039</v>
       </c>
     </row>
     <row r="216">
@@ -10003,10 +11303,13 @@
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>5.294870813108029e-08</v>
+        <v>4.437331274626417e-08</v>
       </c>
       <c r="F216" t="n">
-        <v>5.263684652757123</v>
+        <v>5.29605866949562</v>
+      </c>
+      <c r="G216" t="n">
+        <v>14.96794875692468</v>
       </c>
     </row>
     <row r="217">
@@ -10023,10 +11326,13 @@
         <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>7.469825264475667e-08</v>
+        <v>5.891380596655863e-08</v>
       </c>
       <c r="F217" t="n">
-        <v>5.200086930051826</v>
+        <v>5.244033703621042</v>
+      </c>
+      <c r="G217" t="n">
+        <v>15.04521125266962</v>
       </c>
     </row>
   </sheetData>
